--- a/tests/traces/mi300/resnet_act_checkpoint_recompute_perf_report.xlsx
+++ b/tests/traces/mi300/resnet_act_checkpoint_recompute_perf_report.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_bwd" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coll_analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CONV_bwd" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UnaryElementwise" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Normalization" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Reduce_fwd" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Reduce_bwd" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="coll_analysis" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8838,6 +8840,980 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AK4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>is_recompute</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::sum</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.01907539367675781</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4999500049995</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.002508129256082006</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.00251313472392638</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001128074518469964</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002392902389158245</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002618350655161394</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001253939234117592</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.001256441717791411</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.639808611488654e-05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.001196331561422981</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.001309044423138383</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>thread 639 (pt_autograd_0)</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(23.956999999999997), 'mean_duration_us': np.float64(7.985666666666666), 'median_duration_us': np.float64(7.959), 'std_dev_duration_us': np.float64(0.2945429604583269), 'min_duration_us': np.float64(7.639), 'max_duration_us': np.float64(8.359)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.99)}]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[[10, 1000], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>[[1000, 1], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>['', '[0]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>7.985677083333333</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>7.958984375</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3606049870712312</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>7.63916015625</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8.35888671875</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>23.95703125</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>250880</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00025088</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4785175323486328</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.49999800702325</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.06830178233786818</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07008652134770155</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.003438278962410554</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.06433812772351616</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07048069794238684</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0341507550450699</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.03504312099304324</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.001719132628795248</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.03216893563736539</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0352402085048011</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>thread 542 (python3)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(22.076999999999998), 'mean_duration_us': np.float64(7.358999999999999), 'median_duration_us': np.float64(7.159), 'std_dev_duration_us': np.float64(0.31155523854794487), 'min_duration_us': np.float64(7.119), 'max_duration_us': np.float64(7.799)}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.36)}]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[[10, 512, 7, 7], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>[[25088, 49, 7, 1], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>['', '[-1, -2]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>7.359049479166667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>7.1591796875</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.3813852705988001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.119140625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>7.798828125</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>22.0771484375</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>6390</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.01907539367675781</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4999500049995</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.003323919239960658</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.003226535601764335</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000369630530044365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.003012730455247481</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.003732491662870159</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001661793440636265</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.001613106490233144</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0001847967853436482</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.001506214606163124</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.001866059225512528</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>thread 542 (python3)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.197000000000003), 'mean_duration_us': np.float64(6.065666666666668), 'median_duration_us': np.float64(6.199), 'std_dev_duration_us': np.float64(0.5309948733797302), 'min_duration_us': np.float64(5.359), 'max_duration_us': np.float64(6.639)}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.07)}]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>[[10, 1000], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '', 'c10::BFloat16']</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>[[1000, 1], [], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>['', '[]', 'False', '', '']</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>6.065755208333333</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>6.19921875</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.6504878218749942</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.35888671875</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6.63916015625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>18.197265625</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>6408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AK2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>is_recompute</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>250880</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.00025088</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4785175323486328</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.49999800702325</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.08513929415485562</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.08420260373647985</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.004738044304955399</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0809395538752363</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.09027572485285074</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04256947739679404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.04210113405440839</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.002369012709665562</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.04046961562696912</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.04513768250900465</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>thread 542 (python3)</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(17.716), 'mean_duration_us': np.float64(5.905333333333334), 'median_duration_us': np.float64(5.959), 'std_dev_duration_us': np.float64(0.2644243222969896), 'min_duration_us': np.float64(5.558), 'max_duration_us': np.float64(6.199)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(5.91)}]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>[[10, 512, 7, 7], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>[[25088, 49, 7, 1], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>['', '[-1, -2]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.905436197916667</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>5.958984375</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3238936790067017</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.55810546875</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>6.19921875</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>17.71630859375</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6390</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -24986,10 +25962,10 @@
         <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.649650699141911</v>
+        <v>6.65587054158761</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.649650699141911</v>
+        <v>6.65587054158761</v>
       </c>
     </row>
     <row r="3">
@@ -25146,10 +26122,10 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.490791641814621</v>
+        <v>6.496862893251206</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.14044234095653</v>
+        <v>13.15273343483882</v>
       </c>
     </row>
     <row r="4">
@@ -25306,10 +26282,10 @@
         <v>1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.11290239358264</v>
+        <v>6.118620181101755</v>
       </c>
       <c r="AR4" t="n">
-        <v>19.25334473453917</v>
+        <v>19.27135361594057</v>
       </c>
     </row>
     <row r="5">
@@ -25466,10 +26442,10 @@
         <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.720635127014599</v>
+        <v>5.725986001938595</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.97397986155377</v>
+        <v>24.99733961787916</v>
       </c>
     </row>
     <row r="6">
@@ -25626,10 +26602,10 @@
         <v>1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.711028049499687</v>
+        <v>5.716369938311297</v>
       </c>
       <c r="AR6" t="n">
-        <v>30.68500791105346</v>
+        <v>30.71370955619046</v>
       </c>
     </row>
     <row r="7">
@@ -25786,10 +26762,10 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.882404807506393</v>
+        <v>4.886971632146179</v>
       </c>
       <c r="AR7" t="n">
-        <v>35.56741271855985</v>
+        <v>35.60068118833664</v>
       </c>
     </row>
     <row r="8">
@@ -25946,10 +26922,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.238074091570025</v>
+        <v>3.241102868807852</v>
       </c>
       <c r="AR8" t="n">
-        <v>38.80548681012988</v>
+        <v>38.84178405714449</v>
       </c>
     </row>
     <row r="9">
@@ -26106,10 +27082,10 @@
         <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.938226631284556</v>
+        <v>2.940974942067062</v>
       </c>
       <c r="AR9" t="n">
-        <v>41.74371344141444</v>
+        <v>41.78275899921155</v>
       </c>
     </row>
     <row r="10">
@@ -26266,10 +27242,10 @@
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.541563300162915</v>
+        <v>2.543940586430723</v>
       </c>
       <c r="AR10" t="n">
-        <v>44.28527674157735</v>
+        <v>44.32669958564227</v>
       </c>
     </row>
     <row r="11">
@@ -26426,10 +27402,10 @@
         <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.308143448802054</v>
+        <v>2.31030240259424</v>
       </c>
       <c r="AR11" t="n">
-        <v>46.5934201903794</v>
+        <v>46.63700198823651</v>
       </c>
     </row>
     <row r="12">
@@ -26586,10 +27562,10 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.261761242283137</v>
+        <v>2.263876811839085</v>
       </c>
       <c r="AR12" t="n">
-        <v>48.85518143266254</v>
+        <v>48.9008788000756</v>
       </c>
     </row>
     <row r="13">
@@ -26746,10 +27722,10 @@
         <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.261572639937352</v>
+        <v>2.263688033081496</v>
       </c>
       <c r="AR13" t="n">
-        <v>51.11675407259989</v>
+        <v>51.16456683315709</v>
       </c>
     </row>
     <row r="14">
@@ -26906,10 +27882,10 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.237755190615967</v>
+        <v>2.239848305780569</v>
       </c>
       <c r="AR14" t="n">
-        <v>53.35450926321585</v>
+        <v>53.40441513893766</v>
       </c>
     </row>
     <row r="15">
@@ -27066,10 +28042,10 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.120283870280331</v>
+        <v>2.122267107026136</v>
       </c>
       <c r="AR15" t="n">
-        <v>55.47479313349618</v>
+        <v>55.52668224596379</v>
       </c>
     </row>
     <row r="16">
@@ -27226,10 +28202,10 @@
         <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.103267747527306</v>
+        <v>2.10523506800813</v>
       </c>
       <c r="AR16" t="n">
-        <v>57.57806088102349</v>
+        <v>57.63191731397192</v>
       </c>
     </row>
     <row r="17">
@@ -27386,10 +28362,10 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.075599084873477</v>
+        <v>2.07754052508928</v>
       </c>
       <c r="AR17" t="n">
-        <v>59.65365996589696</v>
+        <v>59.7094578390612</v>
       </c>
     </row>
     <row r="18">
@@ -27546,10 +28522,10 @@
         <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.777472329940292</v>
+        <v>1.779134913186243</v>
       </c>
       <c r="AR18" t="n">
-        <v>61.43113229583726</v>
+        <v>61.48859275224744</v>
       </c>
     </row>
     <row r="19">
@@ -27706,10 +28682,10 @@
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.757291878941323</v>
+        <v>1.758935586124248</v>
       </c>
       <c r="AR19" t="n">
-        <v>63.18842417477858</v>
+        <v>63.24752833837169</v>
       </c>
     </row>
     <row r="20">
@@ -27866,10 +28842,10 @@
         <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.562738081356253</v>
+        <v>1.564199809962717</v>
       </c>
       <c r="AR20" t="n">
-        <v>64.75116225613483</v>
+        <v>64.81172814833441</v>
       </c>
     </row>
     <row r="21">
@@ -28026,10 +29002,10 @@
         <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.425789494076303</v>
+        <v>1.427123125933843</v>
       </c>
       <c r="AR21" t="n">
-        <v>66.17695175021113</v>
+        <v>66.23885127426826</v>
       </c>
     </row>
     <row r="22">
@@ -28186,10 +29162,10 @@
         <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.374661959400481</v>
+        <v>1.375947768413678</v>
       </c>
       <c r="AR22" t="n">
-        <v>67.55161370961162</v>
+        <v>67.61479904268194</v>
       </c>
     </row>
     <row r="23">
@@ -28342,10 +29318,10 @@
         <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.309549910048323</v>
+        <v>1.310774815608601</v>
       </c>
       <c r="AR23" t="n">
-        <v>68.86116361965993</v>
+        <v>68.92557385829053</v>
       </c>
     </row>
     <row r="24">
@@ -28502,10 +29478,10 @@
         <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.203187500721811</v>
+        <v>1.204312918736338</v>
       </c>
       <c r="AR24" t="n">
-        <v>70.06435112038174</v>
+        <v>70.12988677702687</v>
       </c>
     </row>
     <row r="25">
@@ -28662,10 +29638,10 @@
         <v>1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.19078864280448</v>
+        <v>1.191902463376338</v>
       </c>
       <c r="AR25" t="n">
-        <v>71.25513976318622</v>
+        <v>71.32178924040321</v>
       </c>
     </row>
     <row r="26">
@@ -28788,10 +29764,10 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.173807446411787</v>
+        <v>1.174905383387516</v>
       </c>
       <c r="AR26" t="n">
-        <v>72.42894720959801</v>
+        <v>72.49669462379072</v>
       </c>
     </row>
     <row r="27">
@@ -28944,10 +29920,10 @@
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.135812223220237</v>
+        <v>1.136874620840196</v>
       </c>
       <c r="AR27" t="n">
-        <v>73.56475943281825</v>
+        <v>73.63356924463091</v>
       </c>
     </row>
     <row r="28">
@@ -29104,10 +30080,10 @@
         <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.9599975821644955</v>
+        <v>0.9608955291363698</v>
       </c>
       <c r="AR28" t="n">
-        <v>74.52475701498274</v>
+        <v>74.59446477376727</v>
       </c>
     </row>
     <row r="29">
@@ -29264,10 +30240,10 @@
         <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.851586159698594</v>
+        <v>0.8523827025520325</v>
       </c>
       <c r="AR29" t="n">
-        <v>75.37634317468134</v>
+        <v>75.44684747631931</v>
       </c>
     </row>
     <row r="30">
@@ -29424,10 +30400,10 @@
         <v>1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.8464426710339208</v>
+        <v>0.8472344028543348</v>
       </c>
       <c r="AR30" t="n">
-        <v>76.22278584571526</v>
+        <v>76.29408187917365</v>
       </c>
     </row>
     <row r="31">
@@ -29584,10 +30560,10 @@
         <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.8338621960428714</v>
+        <v>0.8346421605425827</v>
       </c>
       <c r="AR31" t="n">
-        <v>77.05664804175814</v>
+        <v>77.12872403971623</v>
       </c>
     </row>
     <row r="32">
@@ -29740,10 +30716,10 @@
         <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.818420087928742</v>
+        <v>0.8191856084397622</v>
       </c>
       <c r="AR32" t="n">
-        <v>77.87506812968688</v>
+        <v>77.947909648156</v>
       </c>
     </row>
     <row r="33">
@@ -29900,10 +30876,10 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.7150077918381473</v>
+        <v>0.715676584232499</v>
       </c>
       <c r="AR33" t="n">
-        <v>78.59007592152503</v>
+        <v>78.6635862323885</v>
       </c>
     </row>
     <row r="34">
@@ -30060,10 +31036,10 @@
         <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.7051096613204809</v>
+        <v>0.7057691953620089</v>
       </c>
       <c r="AR34" t="n">
-        <v>79.29518558284551</v>
+        <v>79.36935542775051</v>
       </c>
     </row>
     <row r="35">
@@ -30220,10 +31196,10 @@
         <v>1</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.6979939975091451</v>
+        <v>0.698646875816439</v>
       </c>
       <c r="AR35" t="n">
-        <v>79.99317958035465</v>
+        <v>80.06800230356694</v>
       </c>
     </row>
     <row r="36">
@@ -30380,10 +31356,10 @@
         <v>1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.6741439502514512</v>
+        <v>0.6747745200882739</v>
       </c>
       <c r="AR36" t="n">
-        <v>80.6673235306061</v>
+        <v>80.74277682365522</v>
       </c>
     </row>
     <row r="37">
@@ -30540,10 +31516,10 @@
         <v>1</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.6577378745921998</v>
+        <v>0.6583530987799998</v>
       </c>
       <c r="AR37" t="n">
-        <v>81.3250614051983</v>
+        <v>81.40112992243522</v>
       </c>
     </row>
     <row r="38">
@@ -30700,10 +31676,10 @@
         <v>1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.6571487833146252</v>
+        <v>0.6577634564877782</v>
       </c>
       <c r="AR38" t="n">
-        <v>81.98221018851292</v>
+        <v>82.05889337892299</v>
       </c>
     </row>
     <row r="39">
@@ -30860,10 +31836,10 @@
         <v>1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.6453227177067147</v>
+        <v>0.6459263292063812</v>
       </c>
       <c r="AR39" t="n">
-        <v>82.62753290621964</v>
+        <v>82.70481970812936</v>
       </c>
     </row>
     <row r="40">
@@ -31020,10 +31996,10 @@
         <v>1</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.6441864467839622</v>
+        <v>0.6447889954569577</v>
       </c>
       <c r="AR40" t="n">
-        <v>83.2717193530036</v>
+        <v>83.34960870358633</v>
       </c>
     </row>
     <row r="41">
@@ -31180,10 +32156,10 @@
         <v>1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.632933173485472</v>
+        <v>0.6335251962541634</v>
       </c>
       <c r="AR41" t="n">
-        <v>83.90465252648907</v>
+        <v>83.9831338998405</v>
       </c>
     </row>
     <row r="42">
@@ -31340,10 +32316,10 @@
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.5954315761865928</v>
+        <v>0.5959885213192978</v>
       </c>
       <c r="AR42" t="n">
-        <v>84.50008410267567</v>
+        <v>84.57912242115979</v>
       </c>
     </row>
     <row r="43">
@@ -31500,10 +32476,10 @@
         <v>1</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.5952266748726539</v>
+        <v>0.5957834283480903</v>
       </c>
       <c r="AR43" t="n">
-        <v>85.09531077754832</v>
+        <v>85.17490584950788</v>
       </c>
     </row>
     <row r="44">
@@ -31660,10 +32636,10 @@
         <v>1</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.5933173671745859</v>
+        <v>0.5938723347527476</v>
       </c>
       <c r="AR44" t="n">
-        <v>85.68862814472291</v>
+        <v>85.76877818426063</v>
       </c>
     </row>
     <row r="45">
@@ -31820,10 +32796,10 @@
         <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5822550246459026</v>
+        <v>0.5827996449094877</v>
       </c>
       <c r="AR45" t="n">
-        <v>86.27088316936882</v>
+        <v>86.35157782917011</v>
       </c>
     </row>
     <row r="46">
@@ -31980,10 +32956,10 @@
         <v>1</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.5533942088927916</v>
+        <v>0.5539118337945207</v>
       </c>
       <c r="AR46" t="n">
-        <v>86.82427737826161</v>
+        <v>86.90548966296463</v>
       </c>
     </row>
     <row r="47">
@@ -32140,10 +33116,10 @@
         <v>1</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.5425903214305539</v>
+        <v>0.5430978407672155</v>
       </c>
       <c r="AR47" t="n">
-        <v>87.36686769969216</v>
+        <v>87.44858750373184</v>
       </c>
     </row>
     <row r="48">
@@ -32266,10 +33242,10 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.4327818445514319</v>
+        <v>0.4331866530155542</v>
       </c>
       <c r="AR48" t="n">
-        <v>87.79964954424359</v>
+        <v>87.8817741567474</v>
       </c>
     </row>
     <row r="49">
@@ -32426,10 +33402,10 @@
         <v>1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.4178566465701941</v>
+        <v>0.4182474945446435</v>
       </c>
       <c r="AR49" t="n">
-        <v>88.21750619081379</v>
+        <v>88.30002165129204</v>
       </c>
     </row>
     <row r="50">
@@ -32586,10 +33562,10 @@
         <v>1</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.39413233420969</v>
+        <v>0.3945009913215375</v>
       </c>
       <c r="AR50" t="n">
-        <v>88.61163852502348</v>
+        <v>88.69452264261358</v>
       </c>
     </row>
     <row r="51">
@@ -32712,10 +33688,10 @@
         <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.3374072681848985</v>
+        <v>0.3377228667242947</v>
       </c>
       <c r="AR51" t="n">
-        <v>88.94904579320838</v>
+        <v>89.03224550933787</v>
       </c>
     </row>
     <row r="52">
@@ -32872,10 +33848,10 @@
         <v>1</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.3217206755484556</v>
+        <v>0.3220216014171924</v>
       </c>
       <c r="AR52" t="n">
-        <v>89.27076646875685</v>
+        <v>89.35426711075506</v>
       </c>
     </row>
     <row r="53">
@@ -33032,10 +34008,10 @@
         <v>1</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.318113946738325</v>
+        <v>0.3184114990035511</v>
       </c>
       <c r="AR53" t="n">
-        <v>89.58888041549517</v>
+        <v>89.67267860975861</v>
       </c>
     </row>
     <row r="54">
@@ -33192,10 +34168,10 @@
         <v>1</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.317906717000364</v>
+        <v>0.3182040754303981</v>
       </c>
       <c r="AR54" t="n">
-        <v>89.90678713249554</v>
+        <v>89.99088268518901</v>
       </c>
     </row>
     <row r="55">
@@ -33352,10 +34328,10 @@
         <v>1</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.3123836952200994</v>
+        <v>0.3126758876155775</v>
       </c>
       <c r="AR55" t="n">
-        <v>90.21917082771564</v>
+        <v>90.30355857280459</v>
       </c>
     </row>
     <row r="56">
@@ -33512,10 +34488,10 @@
         <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.3043599460401704</v>
+        <v>0.304644633311247</v>
       </c>
       <c r="AR56" t="n">
-        <v>90.52353077375581</v>
+        <v>90.60820320611583</v>
       </c>
     </row>
     <row r="57">
@@ -33672,10 +34648,10 @@
         <v>1</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.2989556738850295</v>
+        <v>0.2992353061956489</v>
       </c>
       <c r="AR57" t="n">
-        <v>90.82248644764084</v>
+        <v>90.90743851231149</v>
       </c>
     </row>
     <row r="58">
@@ -33832,10 +34808,10 @@
         <v>1</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.29857846919346</v>
+        <v>0.2988577486804714</v>
       </c>
       <c r="AR58" t="n">
-        <v>91.1210649168343</v>
+        <v>91.20629626099196</v>
       </c>
     </row>
     <row r="59">
@@ -33992,10 +34968,10 @@
         <v>1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.29857846919346</v>
+        <v>0.2988577486804714</v>
       </c>
       <c r="AR59" t="n">
-        <v>91.41964338602776</v>
+        <v>91.50515400967244</v>
       </c>
     </row>
     <row r="60">
@@ -34152,10 +35128,10 @@
         <v>1</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.2925431941283479</v>
+        <v>0.292816828437632</v>
       </c>
       <c r="AR60" t="n">
-        <v>91.7121865801561</v>
+        <v>91.79797083811007</v>
       </c>
     </row>
     <row r="61">
@@ -34312,10 +35288,10 @@
         <v>1</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.289877148623119</v>
+        <v>0.2901482892099889</v>
       </c>
       <c r="AR61" t="n">
-        <v>92.00206372877922</v>
+        <v>92.08811912732007</v>
       </c>
     </row>
     <row r="62">
@@ -34472,10 +35448,10 @@
         <v>1</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.2711799037261863</v>
+        <v>0.2714335555873035</v>
       </c>
       <c r="AR62" t="n">
-        <v>92.27324363250541</v>
+        <v>92.35955268290738</v>
       </c>
     </row>
     <row r="63">
@@ -34632,10 +35608,10 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.2690959642264659</v>
+        <v>0.2693476668460453</v>
       </c>
       <c r="AR63" t="n">
-        <v>92.54233959673188</v>
+        <v>92.62890034975342</v>
       </c>
     </row>
     <row r="64">
@@ -34792,10 +35768,10 @@
         <v>1</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.2637405889757877</v>
+        <v>0.2639872823713036</v>
       </c>
       <c r="AR64" t="n">
-        <v>92.80608018570767</v>
+        <v>92.89288763212473</v>
       </c>
     </row>
     <row r="65">
@@ -34952,10 +35928,10 @@
         <v>1</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.2633773548283505</v>
+        <v>0.2636237084677994</v>
       </c>
       <c r="AR65" t="n">
-        <v>93.06945754053602</v>
+        <v>93.15651134059253</v>
       </c>
     </row>
     <row r="66">
@@ -35112,10 +36088,10 @@
         <v>1</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.2543966233753654</v>
+        <v>0.254634576763852</v>
       </c>
       <c r="AR66" t="n">
-        <v>93.32385416391139</v>
+        <v>93.41114591735638</v>
       </c>
     </row>
     <row r="67">
@@ -35272,10 +36248,10 @@
         <v>1</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.2469992202573635</v>
+        <v>0.2472302543828718</v>
       </c>
       <c r="AR67" t="n">
-        <v>93.57085338416876</v>
+        <v>93.65837617173925</v>
       </c>
     </row>
     <row r="68">
@@ -35432,10 +36408,10 @@
         <v>1</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.2454484898586889</v>
+        <v>0.2456780734871422</v>
       </c>
       <c r="AR68" t="n">
-        <v>93.81630187402745</v>
+        <v>93.90405424522639</v>
       </c>
     </row>
     <row r="69">
@@ -35592,10 +36568,10 @@
         <v>1</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.2441119744700413</v>
+        <v>0.2443403079704023</v>
       </c>
       <c r="AR69" t="n">
-        <v>94.06041384849749</v>
+        <v>94.14839455319679</v>
       </c>
     </row>
     <row r="70">
@@ -35752,10 +36728,10 @@
         <v>1</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.2343861473300055</v>
+        <v>0.2346053836438822</v>
       </c>
       <c r="AR70" t="n">
-        <v>94.29479999582749</v>
+        <v>94.38299993684068</v>
       </c>
     </row>
     <row r="71">
@@ -35912,10 +36888,10 @@
         <v>1</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.2286512389637358</v>
+        <v>0.2288651110520174</v>
       </c>
       <c r="AR71" t="n">
-        <v>94.52345123479122</v>
+        <v>94.61186504789269</v>
       </c>
     </row>
     <row r="72">
@@ -36072,10 +37048,10 @@
         <v>1</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.2210303071396187</v>
+        <v>0.2212370508842653</v>
       </c>
       <c r="AR72" t="n">
-        <v>94.74448154193084</v>
+        <v>94.83310209877696</v>
       </c>
     </row>
     <row r="73">
@@ -36232,10 +37208,10 @@
         <v>1</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.2118586449168268</v>
+        <v>0.2120568098207837</v>
       </c>
       <c r="AR73" t="n">
-        <v>94.95634018684767</v>
+        <v>95.04515890859774</v>
       </c>
     </row>
     <row r="74">
@@ -36392,10 +37368,10 @@
         <v>1</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.2093905154534708</v>
+        <v>0.2095863717585114</v>
       </c>
       <c r="AR74" t="n">
-        <v>95.16573070230113</v>
+        <v>95.25474528035625</v>
       </c>
     </row>
     <row r="75">
@@ -36552,10 +37528,10 @@
         <v>1</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.2069130722940267</v>
+        <v>0.207106611288457</v>
       </c>
       <c r="AR75" t="n">
-        <v>95.37264377459516</v>
+        <v>95.4618518916447</v>
       </c>
     </row>
     <row r="76">
@@ -36712,10 +37688,10 @@
         <v>1</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.2017625983572875</v>
+        <v>0.2019513197849227</v>
       </c>
       <c r="AR76" t="n">
-        <v>95.57440637295245</v>
+        <v>95.66380321142962</v>
       </c>
     </row>
     <row r="77">
@@ -36872,10 +37848,10 @@
         <v>1</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.2006379695546451</v>
+        <v>0.200825639045227</v>
       </c>
       <c r="AR77" t="n">
-        <v>95.7750443425071</v>
+        <v>95.86462885047484</v>
       </c>
     </row>
     <row r="78">
@@ -37032,16 +38008,16 @@
         <v>1</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.1822923166850395</v>
+        <v>0.1824628263163182</v>
       </c>
       <c r="AR78" t="n">
-        <v>95.95733665919214</v>
+        <v>96.04709167679117</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>aten::mse_loss</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -37061,12 +38037,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>thread 542 (python3)</t>
+          <t>thread 639 (pt_autograd_0)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>((10, 1000), (10, 1000), ())</t>
+          <t>((10, 64, 56, 56), (10, 64, 56, 56), ())</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -37076,7 +38052,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>((1000, 1), (1000, 1), ())</t>
+          <t>((200704, 3136, 56, 1), (200704, 3136, 56, 1), ())</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -37085,89 +38061,123 @@
         </is>
       </c>
       <c r="J79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>6404</v>
+        <v>1328</v>
       </c>
       <c r="L79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M79" t="n">
-        <v>78.18000000000001</v>
+        <v>33.39</v>
       </c>
       <c r="N79" t="n">
-        <v>26.06</v>
+        <v>5.565</v>
       </c>
       <c r="O79" t="n">
-        <v>2.977263844539146</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+        <v>0.5423190942609342</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.00200704</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>11.484375</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>1.933152724423313</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.1441950530863484</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.3221921207372188</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0.02403250884772472</v>
+      </c>
       <c r="X79" t="n">
-        <v>12.59798177083333</v>
+        <v>6.258951822916667</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.7331822767157538</v>
+        <v>0.4778209309471366</v>
       </c>
       <c r="Z79" t="n">
-        <v>37.7939453125</v>
+        <v>37.5537109375</v>
       </c>
       <c r="AA79" t="n">
-        <v>27.11</v>
+        <v>5.744999999999999</v>
       </c>
       <c r="AB79" t="n">
-        <v>22.7</v>
+        <v>4.77</v>
       </c>
       <c r="AC79" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
+        <v>6.22</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.911996115601424</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.710773274139845</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.105567106633655</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0.318666019266904</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0.2851288790233074</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0.3509278511056091</v>
+      </c>
       <c r="AJ79" t="n">
-        <v>12.43798828125</v>
+        <v>6.298828125</v>
       </c>
       <c r="AK79" t="n">
-        <v>11.9580078125</v>
+        <v>5.71923828125</v>
       </c>
       <c r="AL79" t="n">
-        <v>13.39794921875</v>
+        <v>7.0390625</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16)#1}, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::mse_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16)#1}, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(19.597), 'mean_duration_us': np.float64(6.532333333333334), 'median_duration_us': np.float64(6.599), 'std_dev_duration_us': np.float64(0.21746008573733472), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(6.759)}, {'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.197000000000003), 'mean_duration_us': np.float64(6.065666666666668), 'median_duration_us': np.float64(6.199), 'std_dev_duration_us': np.float64(0.5309948733797302), 'min_duration_us': np.float64(5.359), 'max_duration_us': np.float64(6.639)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(37.554), 'mean_duration_us': np.float64(6.259), 'median_duration_us': np.float64(6.2989999999999995), 'std_dev_duration_us': np.float64(0.4361956747454822), 'min_duration_us': np.float64(5.719), 'max_duration_us': np.float64(7.039)}]</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::ms...', 'stream': 0, 'mean_duration_us': np.float64(6.53)}, {'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.07)}]</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr"/>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(6.26)}]</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>{'shape_in1': (10, 64, 56, 56), 'shape_in2': (10, 64, 56, 56), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (200704, 3136, 56, 1), 'stride_input2': (200704, 3136, 56, 1), 'stride_output': None}</t>
+        </is>
+      </c>
       <c r="AP79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.1802246761534733</v>
+        <v>0.1792465956314731</v>
       </c>
       <c r="AR79" t="n">
-        <v>96.13756133534561</v>
+        <v>96.22633827242264</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::threshold_backward</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -37192,7 +38202,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>((10, 64, 56, 56), (10, 64, 56, 56), ())</t>
+          <t>((10, 64, 112, 112), (10, 64, 112, 112), ())</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -37202,37 +38212,37 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>((200704, 3136, 56, 1), (200704, 3136, 56, 1), ())</t>
+          <t>((802816, 12544, 112, 1), (802816, 12544, 112, 1), ())</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>('', '', '1')</t>
+          <t>('', '', '0')</t>
         </is>
       </c>
       <c r="J80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1328</v>
+        <v>1600</v>
       </c>
       <c r="L80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M80" t="n">
-        <v>33.39</v>
+        <v>14.97</v>
       </c>
       <c r="N80" t="n">
-        <v>5.565</v>
+        <v>4.989999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>0.5423190942609342</v>
+        <v>0.2535744466621197</v>
       </c>
       <c r="P80" t="n">
-        <v>0.00200704</v>
+        <v>0.008028159999999999</v>
       </c>
       <c r="Q80" t="n">
-        <v>11.484375</v>
+        <v>45.9375</v>
       </c>
       <c r="R80" t="n">
         <v>0.1666666666666667</v>
@@ -37243,91 +38253,91 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>1.933152724423313</v>
+        <v>3.961416641468842</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1441950530863484</v>
+        <v>0.2226697793403497</v>
       </c>
       <c r="V80" t="n">
-        <v>0.3221921207372188</v>
+        <v>0.6602361069114736</v>
       </c>
       <c r="W80" t="n">
-        <v>0.02403250884772472</v>
+        <v>0.03711162989005828</v>
       </c>
       <c r="X80" t="n">
-        <v>6.258951822916667</v>
+        <v>12.18570963541667</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.4778209309471366</v>
+        <v>0.698889002841252</v>
       </c>
       <c r="Z80" t="n">
-        <v>37.5537109375</v>
+        <v>36.55712890625</v>
       </c>
       <c r="AA80" t="n">
-        <v>5.744999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="AB80" t="n">
-        <v>4.77</v>
+        <v>4.81</v>
       </c>
       <c r="AC80" t="n">
-        <v>6.22</v>
+        <v>5.28</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.911996115601424</v>
+        <v>4.014406693253032</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.710773274139845</v>
+        <v>3.71703203014318</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.105567106633655</v>
+        <v>4.152811201010314</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.318666019266904</v>
+        <v>0.6690677822088386</v>
       </c>
       <c r="AH80" t="n">
-        <v>0.2851288790233074</v>
+        <v>0.6195053383571966</v>
       </c>
       <c r="AI80" t="n">
-        <v>0.3509278511056091</v>
+        <v>0.6921352001683856</v>
       </c>
       <c r="AJ80" t="n">
-        <v>6.298828125</v>
+        <v>11.9990234375</v>
       </c>
       <c r="AK80" t="n">
-        <v>5.71923828125</v>
+        <v>11.59912109375</v>
       </c>
       <c r="AL80" t="n">
-        <v>7.0390625</v>
+        <v>12.958984375</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(37.554), 'mean_duration_us': np.float64(6.259), 'median_duration_us': np.float64(6.2989999999999995), 'std_dev_duration_us': np.float64(0.4361956747454822), 'min_duration_us': np.float64(5.719), 'max_duration_us': np.float64(7.039)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::(anonymous namespace)::threshold_kernel_impl&lt;c10::BFloat16&gt;(at::TensorIteratorBase&amp;, c10::BFloat16, c10::BFloat16)::{lambda(c10::BFloat16, c10::BFloat16)#1}&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::(anonymous namespace)::threshold_kernel_impl&lt;c10::BFloat16&gt;(at::TensorIteratorBase&amp;, c10::BFloat16, c10::BFloat16)::{lambda(c10::BFloat16, c10::BFloat16)#1}&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(36.557), 'mean_duration_us': np.float64(12.185666666666668), 'median_duration_us': np.float64(11.999), 'std_dev_duration_us': np.float64(0.5706915882408716), 'min_duration_us': np.float64(11.599), 'max_duration_us': np.float64(12.959)}]</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(6.26)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(12.19)}]</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 64, 56, 56), 'shape_in2': (10, 64, 56, 56), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (200704, 3136, 56, 1), 'stride_input2': (200704, 3136, 56, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (10, 64, 112, 112), 'shape_in2': (10, 64, 112, 112), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (802816, 12544, 112, 1), 'stride_input2': (802816, 12544, 112, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP80" t="b">
         <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.1790790915346326</v>
+        <v>0.1744898370606262</v>
       </c>
       <c r="AR80" t="n">
-        <v>96.31664042688024</v>
+        <v>96.40082810948326</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>aten::threshold_backward</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -37352,50 +38362,50 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>((10, 64, 112, 112), (10, 64, 112, 112), ())</t>
+          <t>((512, 512, 3, 3), (), (512, 512, 3, 3))</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>((802816, 12544, 112, 1), (802816, 12544, 112, 1), ())</t>
+          <t>((4608, 9, 3, 1), (), (4608, 9, 3, 1))</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>('', '', '0')</t>
+          <t>('', '', '')</t>
         </is>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1600</v>
+        <v>272</v>
       </c>
       <c r="L81" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M81" t="n">
-        <v>14.97</v>
+        <v>47.149</v>
       </c>
       <c r="N81" t="n">
-        <v>4.989999999999999</v>
+        <v>5.238777777777778</v>
       </c>
       <c r="O81" t="n">
-        <v>0.2535744466621197</v>
+        <v>0.5600678034349453</v>
       </c>
       <c r="P81" t="n">
-        <v>0.008028159999999999</v>
+        <v>0.002359296</v>
       </c>
       <c r="Q81" t="n">
-        <v>45.9375</v>
+        <v>9.000007629394531</v>
       </c>
       <c r="R81" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2499997880725538</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -37403,91 +38413,91 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>3.961416641468842</v>
+        <v>2.678721735357199</v>
       </c>
       <c r="U81" t="n">
-        <v>0.2226697793403497</v>
+        <v>0.6836274955838052</v>
       </c>
       <c r="V81" t="n">
-        <v>0.6602361069114736</v>
+        <v>0.6696798661446434</v>
       </c>
       <c r="W81" t="n">
-        <v>0.03711162989005828</v>
+        <v>0.170906729016522</v>
       </c>
       <c r="X81" t="n">
-        <v>12.18570963541667</v>
+        <v>3.710177951388889</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.698889002841252</v>
+        <v>0.8288603382936338</v>
       </c>
       <c r="Z81" t="n">
-        <v>36.55712890625</v>
+        <v>33.3916015625</v>
       </c>
       <c r="AA81" t="n">
-        <v>4.88</v>
+        <v>5.13</v>
       </c>
       <c r="AB81" t="n">
-        <v>4.81</v>
+        <v>4.55</v>
       </c>
       <c r="AC81" t="n">
-        <v>5.28</v>
+        <v>6.26</v>
       </c>
       <c r="AD81" t="n">
-        <v>4.014406693253032</v>
+        <v>2.359874141147741</v>
       </c>
       <c r="AE81" t="n">
-        <v>3.71703203014318</v>
+        <v>2.03424578633828</v>
       </c>
       <c r="AF81" t="n">
-        <v>4.152811201010314</v>
+        <v>3.630916628968627</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.6690677822088386</v>
+        <v>0.5899680351648352</v>
       </c>
       <c r="AH81" t="n">
-        <v>0.6195053383571966</v>
+        <v>0.5085610154720555</v>
       </c>
       <c r="AI81" t="n">
-        <v>0.6921352001683856</v>
+        <v>0.9077283877512681</v>
       </c>
       <c r="AJ81" t="n">
-        <v>11.9990234375</v>
+        <v>3.9990234375</v>
       </c>
       <c r="AK81" t="n">
-        <v>11.59912109375</v>
+        <v>2.59912109375</v>
       </c>
       <c r="AL81" t="n">
-        <v>12.958984375</v>
+        <v>4.63916015625</v>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::(anonymous namespace)::threshold_kernel_impl&lt;c10::BFloat16&gt;(at::TensorIteratorBase&amp;, c10::BFloat16, c10::BFloat16)::{lambda(c10::BFloat16, c10::BFloat16)#1}&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::(anonymous namespace)::threshold_kernel_impl&lt;c10::BFloat16&gt;(at::TensorIteratorBase&amp;, c10::BFloat16, c10::BFloat16)::{lambda(c10::BFloat16, c10::BFloat16)#1}&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(36.557), 'mean_duration_us': np.float64(12.185666666666668), 'median_duration_us': np.float64(11.999), 'std_dev_duration_us': np.float64(0.5706915882408716), 'min_duration_us': np.float64(11.599), 'max_duration_us': np.float64(12.959)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(33.391), 'mean_duration_us': np.float64(3.710111111111111), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.7815148316562939), 'min_duration_us': np.float64(2.599), 'max_duration_us': np.float64(4.639)}]</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(12.19)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(3.71)}]</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 64, 112, 112), 'shape_in2': (10, 64, 112, 112), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (802816, 12544, 112, 1), 'stride_input2': (802816, 12544, 112, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (512, 512, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (4608, 9, 3, 1), 'stride_input2': (), 'stride_output': (4608, 9, 3, 1)}</t>
         </is>
       </c>
       <c r="AP81" t="b">
         <v>1</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.1743267781056613</v>
+        <v>0.1593805446476911</v>
       </c>
       <c r="AR81" t="n">
-        <v>96.49096720498591</v>
+        <v>96.56020865413095</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -37507,55 +38517,55 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>thread 639 (pt_autograd_0)</t>
+          <t>thread 542 (python3)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>((512, 512, 3, 3), (), (512, 512, 3, 3))</t>
+          <t>((10, 128, 28, 28), (10, 128, 28, 28), ())</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>((4608, 9, 3, 1), (), (4608, 9, 3, 1))</t>
+          <t>((100352, 784, 28, 1), (100352, 784, 28, 1), ())</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>('', '', '')</t>
+          <t>('', '', '1')</t>
         </is>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>272</v>
+        <v>6074</v>
       </c>
       <c r="L82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M82" t="n">
-        <v>47.149</v>
+        <v>38.81</v>
       </c>
       <c r="N82" t="n">
-        <v>5.238777777777778</v>
+        <v>6.468333333333334</v>
       </c>
       <c r="O82" t="n">
-        <v>0.5600678034349453</v>
+        <v>1.091025511464634</v>
       </c>
       <c r="P82" t="n">
-        <v>0.002359296</v>
+        <v>0.00100352</v>
       </c>
       <c r="Q82" t="n">
-        <v>9.000007629394531</v>
+        <v>5.7421875</v>
       </c>
       <c r="R82" t="n">
-        <v>0.2499997880725538</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -37563,85 +38573,85 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>2.678721735357199</v>
+        <v>1.121969465301464</v>
       </c>
       <c r="U82" t="n">
-        <v>0.6836274955838052</v>
+        <v>0.1565497164384003</v>
       </c>
       <c r="V82" t="n">
-        <v>0.6696798661446434</v>
+        <v>0.1869949108835773</v>
       </c>
       <c r="W82" t="n">
-        <v>0.170906729016522</v>
+        <v>0.02609161940640006</v>
       </c>
       <c r="X82" t="n">
-        <v>3.710177951388889</v>
+        <v>5.445638020833333</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.8288603382936338</v>
+        <v>0.6823692762967902</v>
       </c>
       <c r="Z82" t="n">
-        <v>33.3916015625</v>
+        <v>32.673828125</v>
       </c>
       <c r="AA82" t="n">
-        <v>5.13</v>
+        <v>6.81</v>
       </c>
       <c r="AB82" t="n">
-        <v>4.55</v>
+        <v>4.89</v>
       </c>
       <c r="AC82" t="n">
-        <v>6.26</v>
+        <v>7.75</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.359874141147741</v>
+        <v>1.049473595342813</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.03424578633828</v>
+        <v>0.9904621493975905</v>
       </c>
       <c r="AF82" t="n">
-        <v>3.630916628968627</v>
+        <v>1.394149661955907</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.5899680351648352</v>
+        <v>0.1749122658904688</v>
       </c>
       <c r="AH82" t="n">
-        <v>0.5085610154720555</v>
+        <v>0.1650770248995984</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.9077283877512681</v>
+        <v>0.2323582769926512</v>
       </c>
       <c r="AJ82" t="n">
-        <v>3.9990234375</v>
+        <v>5.739013671875</v>
       </c>
       <c r="AK82" t="n">
-        <v>2.59912109375</v>
+        <v>4.31884765625</v>
       </c>
       <c r="AL82" t="n">
-        <v>4.63916015625</v>
+        <v>6.0791015625</v>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(33.391), 'mean_duration_us': np.float64(3.710111111111111), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.7815148316562939), 'min_duration_us': np.float64(2.599), 'max_duration_us': np.float64(4.639)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.674), 'mean_duration_us': np.float64(5.445666666666667), 'median_duration_us': np.float64(5.739000000000001), 'std_dev_duration_us': np.float64(0.6228607834464742), 'min_duration_us': np.float64(4.319), 'max_duration_us': np.float64(6.079)}]</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(3.71)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.45)}]</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>{'shape_in1': (512, 512, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (4608, 9, 3, 1), 'stride_input2': (), 'stride_output': (4608, 9, 3, 1)}</t>
+          <t>{'shape_in1': (10, 128, 28, 28), 'shape_in2': (10, 128, 28, 28), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (100352, 784, 28, 1), 'stride_input2': (100352, 784, 28, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP82" t="b">
         <v>1</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.1592316051708151</v>
+        <v>0.1559545597877474</v>
       </c>
       <c r="AR82" t="n">
-        <v>96.65019881015672</v>
+        <v>96.71616321391869</v>
       </c>
     </row>
     <row r="83">
@@ -37672,7 +38682,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>((10, 128, 28, 28), (10, 128, 28, 28), ())</t>
+          <t>((10, 512, 7, 7), (10, 512, 7, 7), ())</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -37682,7 +38692,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>((100352, 784, 28, 1), (100352, 784, 28, 1), ())</t>
+          <t>((25088, 49, 7, 1), (25088, 49, 7, 1), ())</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -37694,25 +38704,25 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>6074</v>
+        <v>6332</v>
       </c>
       <c r="L83" t="n">
         <v>6</v>
       </c>
       <c r="M83" t="n">
-        <v>38.81</v>
+        <v>36.2</v>
       </c>
       <c r="N83" t="n">
-        <v>6.468333333333334</v>
+        <v>6.033333333333334</v>
       </c>
       <c r="O83" t="n">
-        <v>1.091025511464634</v>
+        <v>1.155225807652628</v>
       </c>
       <c r="P83" t="n">
-        <v>0.00100352</v>
+        <v>0.00025088</v>
       </c>
       <c r="Q83" t="n">
-        <v>5.7421875</v>
+        <v>1.435546875</v>
       </c>
       <c r="R83" t="n">
         <v>0.1666666666666667</v>
@@ -37723,85 +38733,85 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>1.121969465301464</v>
+        <v>0.2886959041489444</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1565497164384003</v>
+        <v>0.05652407689825793</v>
       </c>
       <c r="V83" t="n">
-        <v>0.1869949108835773</v>
+        <v>0.04811598402482407</v>
       </c>
       <c r="W83" t="n">
-        <v>0.02609161940640006</v>
+        <v>0.009420679483042991</v>
       </c>
       <c r="X83" t="n">
-        <v>5.445638020833333</v>
+        <v>5.399007161458333</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.6823692762967902</v>
+        <v>1.146224251155981</v>
       </c>
       <c r="Z83" t="n">
-        <v>32.673828125</v>
+        <v>32.39404296875</v>
       </c>
       <c r="AA83" t="n">
-        <v>6.81</v>
+        <v>6.16</v>
       </c>
       <c r="AB83" t="n">
-        <v>4.89</v>
+        <v>4.54</v>
       </c>
       <c r="AC83" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.049473595342813</v>
+        <v>0.2924459792266926</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.9904621493975905</v>
+        <v>0.2068030750654055</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.394149661955907</v>
+        <v>0.3517988634029442</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.1749122658904688</v>
+        <v>0.04874099653778209</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.1650770248995984</v>
+        <v>0.03446717917756759</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.2323582769926512</v>
+        <v>0.05863314390049069</v>
       </c>
       <c r="AJ83" t="n">
-        <v>5.739013671875</v>
+        <v>5.19921875</v>
       </c>
       <c r="AK83" t="n">
-        <v>4.31884765625</v>
+        <v>4.27880859375</v>
       </c>
       <c r="AL83" t="n">
-        <v>6.0791015625</v>
+        <v>7.27880859375</v>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.674), 'mean_duration_us': np.float64(5.445666666666667), 'median_duration_us': np.float64(5.739000000000001), 'std_dev_duration_us': np.float64(0.6228607834464742), 'min_duration_us': np.float64(4.319), 'max_duration_us': np.float64(6.079)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.394000000000005), 'mean_duration_us': np.float64(5.399000000000001), 'median_duration_us': np.float64(5.199), 'std_dev_duration_us': np.float64(1.0463906217724492), 'min_duration_us': np.float64(4.279), 'max_duration_us': np.float64(7.279)}]</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.45)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.4)}]</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 128, 28, 28), 'shape_in2': (10, 128, 28, 28), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (100352, 784, 28, 1), 'stride_input2': (100352, 784, 28, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (10, 512, 7, 7), 'shape_in2': (10, 512, 7, 7), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (25088, 49, 7, 1), 'stride_input2': (25088, 49, 7, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP83" t="b">
         <v>1</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.1558088218584251</v>
+        <v>0.1546191248729531</v>
       </c>
       <c r="AR83" t="n">
-        <v>96.80600763201515</v>
+        <v>96.87078233879164</v>
       </c>
     </row>
     <row r="84">
@@ -37832,7 +38842,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>((10, 512, 7, 7), (10, 512, 7, 7), ())</t>
+          <t>((10, 256, 14, 14), (10, 256, 14, 14), ())</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -37842,7 +38852,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>((25088, 49, 7, 1), (25088, 49, 7, 1), ())</t>
+          <t>((50176, 196, 14, 1), (50176, 196, 14, 1), ())</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -37854,25 +38864,25 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>6332</v>
+        <v>6203</v>
       </c>
       <c r="L84" t="n">
         <v>6</v>
       </c>
       <c r="M84" t="n">
-        <v>36.2</v>
+        <v>43.78</v>
       </c>
       <c r="N84" t="n">
-        <v>6.033333333333334</v>
+        <v>7.296666666666667</v>
       </c>
       <c r="O84" t="n">
-        <v>1.155225807652628</v>
+        <v>1.244952475665905</v>
       </c>
       <c r="P84" t="n">
-        <v>0.00025088</v>
+        <v>0.00050176</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.435546875</v>
+        <v>2.87109375</v>
       </c>
       <c r="R84" t="n">
         <v>0.1666666666666667</v>
@@ -37883,85 +38893,85 @@
         </is>
       </c>
       <c r="T84" t="n">
-        <v>0.2886959041489444</v>
+        <v>0.5606019905108158</v>
       </c>
       <c r="U84" t="n">
-        <v>0.05652407689825793</v>
+        <v>0.04027434784488856</v>
       </c>
       <c r="V84" t="n">
-        <v>0.04811598402482407</v>
+        <v>0.09343366508513595</v>
       </c>
       <c r="W84" t="n">
-        <v>0.009420679483042991</v>
+        <v>0.006712391307481421</v>
       </c>
       <c r="X84" t="n">
-        <v>5.399007161458333</v>
+        <v>5.392252604166667</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.146224251155981</v>
+        <v>0.3687834988480689</v>
       </c>
       <c r="Z84" t="n">
-        <v>32.39404296875</v>
+        <v>32.353515625</v>
       </c>
       <c r="AA84" t="n">
-        <v>6.16</v>
+        <v>7.21</v>
       </c>
       <c r="AB84" t="n">
-        <v>4.54</v>
+        <v>5.66</v>
       </c>
       <c r="AC84" t="n">
-        <v>7.72</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.2924459792266926</v>
+        <v>0.5577447396569328</v>
       </c>
       <c r="AE84" t="n">
-        <v>0.2068030750654055</v>
+        <v>0.5156068640240843</v>
       </c>
       <c r="AF84" t="n">
-        <v>0.3517988634029442</v>
+        <v>0.6326315288323415</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.04874099653778209</v>
+        <v>0.0929574566094888</v>
       </c>
       <c r="AH84" t="n">
-        <v>0.03446717917756759</v>
+        <v>0.08593447733734738</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.05863314390049069</v>
+        <v>0.1054385881387236</v>
       </c>
       <c r="AJ84" t="n">
-        <v>5.19921875</v>
+        <v>5.39892578125</v>
       </c>
       <c r="AK84" t="n">
-        <v>4.27880859375</v>
+        <v>4.7587890625</v>
       </c>
       <c r="AL84" t="n">
-        <v>7.27880859375</v>
+        <v>5.8388671875</v>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.394000000000005), 'mean_duration_us': np.float64(5.399000000000001), 'median_duration_us': np.float64(5.199), 'std_dev_duration_us': np.float64(1.0463906217724492), 'min_duration_us': np.float64(4.279), 'max_duration_us': np.float64(7.279)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.354), 'mean_duration_us': np.float64(5.392333333333333), 'median_duration_us': np.float64(5.399), 'std_dev_duration_us': np.float64(0.33658414830304906), 'min_duration_us': np.float64(4.759), 'max_duration_us': np.float64(5.839)}]</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.4)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.39)}]</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 512, 7, 7), 'shape_in2': (10, 512, 7, 7), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (25088, 49, 7, 1), 'stride_input2': (25088, 49, 7, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (10, 256, 14, 14), 'shape_in2': (10, 256, 14, 14), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (50176, 196, 14, 1), 'stride_input2': (50176, 196, 14, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP84" t="b">
         <v>1</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.1544746348937996</v>
+        <v>0.1544256849114732</v>
       </c>
       <c r="AR84" t="n">
-        <v>96.96048226690895</v>
+        <v>97.02520802370312</v>
       </c>
     </row>
     <row r="85">
@@ -37987,12 +38997,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>thread 542 (python3)</t>
+          <t>thread 639 (pt_autograd_0)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>((10, 256, 14, 14), (10, 256, 14, 14), ())</t>
+          <t>((10, 512, 7, 7), (10, 512, 7, 7), ())</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -38002,7 +39012,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>((50176, 196, 14, 1), (50176, 196, 14, 1), ())</t>
+          <t>((25088, 49, 7, 1), (25088, 49, 7, 1), ())</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -38011,28 +39021,28 @@
         </is>
       </c>
       <c r="J85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" t="n">
-        <v>6203</v>
+        <v>153</v>
       </c>
       <c r="L85" t="n">
         <v>6</v>
       </c>
       <c r="M85" t="n">
-        <v>43.78</v>
+        <v>38.639</v>
       </c>
       <c r="N85" t="n">
-        <v>7.296666666666667</v>
+        <v>6.439833333333334</v>
       </c>
       <c r="O85" t="n">
-        <v>1.244952475665905</v>
+        <v>1.232876379312486</v>
       </c>
       <c r="P85" t="n">
-        <v>0.00050176</v>
+        <v>0.00025088</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.87109375</v>
+        <v>1.435546875</v>
       </c>
       <c r="R85" t="n">
         <v>0.1666666666666667</v>
@@ -38043,91 +39053,91 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>0.5606019905108158</v>
+        <v>0.2952255693218805</v>
       </c>
       <c r="U85" t="n">
-        <v>0.04027434784488856</v>
+        <v>0.04730936028781432</v>
       </c>
       <c r="V85" t="n">
-        <v>0.09343366508513595</v>
+        <v>0.04920426155364675</v>
       </c>
       <c r="W85" t="n">
-        <v>0.006712391307481421</v>
+        <v>0.007884893381302379</v>
       </c>
       <c r="X85" t="n">
-        <v>5.392252604166667</v>
+        <v>5.212483723958333</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.3687834988480689</v>
+        <v>0.8603393923316893</v>
       </c>
       <c r="Z85" t="n">
-        <v>32.353515625</v>
+        <v>31.27490234375</v>
       </c>
       <c r="AA85" t="n">
-        <v>7.21</v>
+        <v>6.574999999999999</v>
       </c>
       <c r="AB85" t="n">
-        <v>5.66</v>
+        <v>5.07</v>
       </c>
       <c r="AC85" t="n">
-        <v>9.119999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.5577447396569328</v>
+        <v>0.2988888743499623</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.5156068640240843</v>
+        <v>0.2294955289213132</v>
       </c>
       <c r="AF85" t="n">
-        <v>0.6326315288323415</v>
+        <v>0.3619175205447289</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.0929574566094888</v>
+        <v>0.04981481239166036</v>
       </c>
       <c r="AH85" t="n">
-        <v>0.08593447733734738</v>
+        <v>0.03824925482021886</v>
       </c>
       <c r="AI85" t="n">
-        <v>0.1054385881387236</v>
+        <v>0.0603195867574548</v>
       </c>
       <c r="AJ85" t="n">
-        <v>5.39892578125</v>
+        <v>5.05908203125</v>
       </c>
       <c r="AK85" t="n">
-        <v>4.7587890625</v>
+        <v>4.1591796875</v>
       </c>
       <c r="AL85" t="n">
-        <v>5.8388671875</v>
+        <v>6.55908203125</v>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(32.354), 'mean_duration_us': np.float64(5.392333333333333), 'median_duration_us': np.float64(5.399), 'std_dev_duration_us': np.float64(0.33658414830304906), 'min_duration_us': np.float64(4.759), 'max_duration_us': np.float64(5.839)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(31.274), 'mean_duration_us': np.float64(5.2123333333333335), 'median_duration_us': np.float64(5.059), 'std_dev_duration_us': np.float64(0.7854227453345676), 'min_duration_us': np.float64(4.159), 'max_duration_us': np.float64(6.559)}]</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.39)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.21)}]</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 256, 14, 14), 'shape_in2': (10, 256, 14, 14), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (50176, 196, 14, 1), 'stride_input2': (50176, 196, 14, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (10, 512, 7, 7), 'shape_in2': (10, 512, 7, 7), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (25088, 49, 7, 1), 'stride_input2': (25088, 49, 7, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP85" t="b">
         <v>1</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.1542813756999708</v>
+        <v>0.1492773852137756</v>
       </c>
       <c r="AR85" t="n">
-        <v>97.11476364260892</v>
+        <v>97.17448540891689</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -38152,50 +39162,50 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>((10, 512, 7, 7), (10, 512, 7, 7), ())</t>
+          <t>((64, 64, 3, 3), (), (64, 64, 3, 3))</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>((25088, 49, 7, 1), (25088, 49, 7, 1), ())</t>
+          <t>((576, 9, 3, 1), (), (576, 9, 3, 1))</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>('', '', '1')</t>
+          <t>('', '', '')</t>
         </is>
       </c>
       <c r="J86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>153</v>
+        <v>1447</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
-        <v>38.639</v>
+        <v>53.01</v>
       </c>
       <c r="N86" t="n">
-        <v>6.439833333333334</v>
+        <v>4.4175</v>
       </c>
       <c r="O86" t="n">
-        <v>1.232876379312486</v>
+        <v>0.3767595085365822</v>
       </c>
       <c r="P86" t="n">
-        <v>0.00025088</v>
+        <v>3.6864e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.435546875</v>
+        <v>0.1406326293945312</v>
       </c>
       <c r="R86" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2499864373677643</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -38203,91 +39213,91 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>0.2952255693218805</v>
+        <v>0.06668872402117339</v>
       </c>
       <c r="U86" t="n">
-        <v>0.04730936028781432</v>
+        <v>0.02610786112406582</v>
       </c>
       <c r="V86" t="n">
-        <v>0.04920426155364675</v>
+        <v>0.01667127653065518</v>
       </c>
       <c r="W86" t="n">
-        <v>0.007884893381302379</v>
+        <v>0.006526611189697569</v>
       </c>
       <c r="X86" t="n">
-        <v>5.212483723958333</v>
+        <v>2.5723876953125</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.8603393923316893</v>
+        <v>1.009306584473318</v>
       </c>
       <c r="Z86" t="n">
-        <v>31.27490234375</v>
+        <v>30.86865234375</v>
       </c>
       <c r="AA86" t="n">
-        <v>6.574999999999999</v>
+        <v>4.38</v>
       </c>
       <c r="AB86" t="n">
-        <v>5.07</v>
+        <v>3.78</v>
       </c>
       <c r="AC86" t="n">
-        <v>7.75</v>
+        <v>5.08</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.2988888743499623</v>
+        <v>0.06586034554800356</v>
       </c>
       <c r="AE86" t="n">
-        <v>0.2294955289213132</v>
+        <v>0.03923178383995843</v>
       </c>
       <c r="AF86" t="n">
-        <v>0.3619175205447289</v>
+        <v>0.09458386219855935</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.04981481239166036</v>
+        <v>0.01646419314735531</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.03824925482021886</v>
+        <v>0.009807413873733437</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.0603195867574548</v>
+        <v>0.02364468274350141</v>
       </c>
       <c r="AJ86" t="n">
-        <v>5.05908203125</v>
+        <v>2.51904296875</v>
       </c>
       <c r="AK86" t="n">
-        <v>4.1591796875</v>
+        <v>1.55908203125</v>
       </c>
       <c r="AL86" t="n">
-        <v>6.55908203125</v>
+        <v>3.7587890625</v>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(31.274), 'mean_duration_us': np.float64(5.2123333333333335), 'median_duration_us': np.float64(5.059), 'std_dev_duration_us': np.float64(0.7854227453345676), 'min_duration_us': np.float64(4.159), 'max_duration_us': np.float64(6.559)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(30.868), 'mean_duration_us': np.float64(2.5723333333333334), 'median_duration_us': np.float64(2.519), 'std_dev_duration_us': np.float64(0.9664137600197731), 'min_duration_us': np.float64(1.559), 'max_duration_us': np.float64(3.759)}]</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(5.21)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.57)}]</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 512, 7, 7), 'shape_in2': (10, 512, 7, 7), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (25088, 49, 7, 1), 'stride_input2': (25088, 49, 7, 1), 'stride_output': None}</t>
+          <t>{'shape_in1': (64, 64, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (576, 9, 3, 1), 'stride_input2': (), 'stride_output': (576, 9, 3, 1)}</t>
         </is>
       </c>
       <c r="AP86" t="b">
         <v>1</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.1491378870352978</v>
+        <v>0.1473383243950865</v>
       </c>
       <c r="AR86" t="n">
-        <v>97.26390152964422</v>
+        <v>97.32182373331199</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38312,50 +39322,50 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>((64, 64, 3, 3), (), (64, 64, 3, 3))</t>
+          <t>((10, 128, 28, 28), (10, 128, 28, 28), ())</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>((576, 9, 3, 1), (), (576, 9, 3, 1))</t>
+          <t>((100352, 784, 28, 1), (100352, 784, 28, 1), ())</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>('', '', '')</t>
+          <t>('', '', '1')</t>
         </is>
       </c>
       <c r="J87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1447</v>
+        <v>956</v>
       </c>
       <c r="L87" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M87" t="n">
-        <v>53.01</v>
+        <v>37.06</v>
       </c>
       <c r="N87" t="n">
-        <v>4.4175</v>
+        <v>6.176666666666667</v>
       </c>
       <c r="O87" t="n">
-        <v>0.3767595085365822</v>
+        <v>0.7811956647771842</v>
       </c>
       <c r="P87" t="n">
-        <v>3.6864e-05</v>
+        <v>0.00100352</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.1406326293945312</v>
+        <v>5.7421875</v>
       </c>
       <c r="R87" t="n">
-        <v>0.2499864373677643</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -38363,96 +39373,96 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>0.06668872402117339</v>
+        <v>1.22715017000074</v>
       </c>
       <c r="U87" t="n">
-        <v>0.02610786112406582</v>
+        <v>0.09870807605136768</v>
       </c>
       <c r="V87" t="n">
-        <v>0.01667127653065518</v>
+        <v>0.2045250283334566</v>
       </c>
       <c r="W87" t="n">
-        <v>0.006526611189697569</v>
+        <v>0.01645134600856128</v>
       </c>
       <c r="X87" t="n">
-        <v>2.5723876953125</v>
+        <v>4.932210286458333</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.009306584473318</v>
+        <v>0.3833994096668192</v>
       </c>
       <c r="Z87" t="n">
-        <v>30.86865234375</v>
+        <v>29.59326171875</v>
       </c>
       <c r="AA87" t="n">
-        <v>4.38</v>
+        <v>6.494999999999999</v>
       </c>
       <c r="AB87" t="n">
-        <v>3.78</v>
+        <v>4.92</v>
       </c>
       <c r="AC87" t="n">
-        <v>5.08</v>
+        <v>6.84</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.06586034554800356</v>
+        <v>1.229089972137329</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.03923178383995843</v>
+        <v>1.115244077055259</v>
       </c>
       <c r="AF87" t="n">
-        <v>0.09458386219855935</v>
+        <v>1.394149661955907</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.01646419314735531</v>
+        <v>0.2048483286895548</v>
       </c>
       <c r="AH87" t="n">
-        <v>0.009807413873733437</v>
+        <v>0.1858740128425432</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.02364468274350141</v>
+        <v>0.2323582769926512</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.51904296875</v>
+        <v>4.89892578125</v>
       </c>
       <c r="AK87" t="n">
-        <v>1.55908203125</v>
+        <v>4.31884765625</v>
       </c>
       <c r="AL87" t="n">
-        <v>3.7587890625</v>
+        <v>5.39892578125</v>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 12, 'total_duration_us': np.float64(30.868), 'mean_duration_us': np.float64(2.5723333333333334), 'median_duration_us': np.float64(2.519), 'std_dev_duration_us': np.float64(0.9664137600197731), 'min_duration_us': np.float64(1.559), 'max_duration_us': np.float64(3.759)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(29.593999999999998), 'mean_duration_us': np.float64(4.932333333333333), 'median_duration_us': np.float64(4.898999999999999), 'std_dev_duration_us': np.float64(0.3499841266241783), 'min_duration_us': np.float64(4.319), 'max_duration_us': np.float64(5.399)}]</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.57)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.93)}]</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>{'shape_in1': (64, 64, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (576, 9, 3, 1), 'stride_input2': (), 'stride_output': (576, 9, 3, 1)}</t>
+          <t>{'shape_in1': (10, 128, 28, 28), 'shape_in2': (10, 128, 28, 28), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (100352, 784, 28, 1), 'stride_input2': (100352, 784, 28, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP87" t="b">
         <v>1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.1472006382489655</v>
+        <v>0.1412507921133362</v>
       </c>
       <c r="AR87" t="n">
-        <v>97.41110216789318</v>
+        <v>97.46307452542533</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::mm</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>elementwise</t>
+          <t>GEMM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -38472,147 +39482,147 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>((10, 128, 28, 28), (10, 128, 28, 28), ())</t>
+          <t>((10, 1000), (1000, 512))</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>((100352, 784, 28, 1), (100352, 784, 28, 1), ())</t>
+          <t>((1000, 1), (512, 1))</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>('', '', '1')</t>
+          <t>('', '')</t>
         </is>
       </c>
       <c r="J88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>956</v>
+        <v>16</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>37.06</v>
+        <v>438.926</v>
       </c>
       <c r="N88" t="n">
-        <v>6.176666666666667</v>
+        <v>146.3086666666667</v>
       </c>
       <c r="O88" t="n">
-        <v>0.7811956647771842</v>
+        <v>166.7726001186446</v>
       </c>
       <c r="P88" t="n">
-        <v>0.00100352</v>
+        <v>0.01024</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.7421875</v>
+        <v>1.005401611328125</v>
       </c>
       <c r="R88" t="n">
-        <v>0.1666666666666667</v>
+        <v>9.713158294126574</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>matrix_bf16</t>
         </is>
       </c>
       <c r="T88" t="n">
-        <v>1.22715017000074</v>
+        <v>0.1193665053856046</v>
       </c>
       <c r="U88" t="n">
-        <v>0.09870807605136768</v>
+        <v>0.009195732100480506</v>
       </c>
       <c r="V88" t="n">
-        <v>0.2045250283334566</v>
+        <v>1.15942576182709</v>
       </c>
       <c r="W88" t="n">
-        <v>0.01645134600856128</v>
+        <v>0.08931960152234825</v>
       </c>
       <c r="X88" t="n">
-        <v>4.932210286458333</v>
+        <v>8.86572265625</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.3833994096668192</v>
+        <v>0.6575774436567361</v>
       </c>
       <c r="Z88" t="n">
-        <v>29.59326171875</v>
+        <v>26.59716796875</v>
       </c>
       <c r="AA88" t="n">
-        <v>6.494999999999999</v>
+        <v>58.159</v>
       </c>
       <c r="AB88" t="n">
-        <v>4.92</v>
+        <v>42.109</v>
       </c>
       <c r="AC88" t="n">
-        <v>6.84</v>
+        <v>338.658</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.229089972137329</v>
+        <v>0.1156073848789891</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.115244077055259</v>
+        <v>0.1126458767673606</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.394149661955907</v>
+        <v>0.1298462545104643</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.2048483286895548</v>
+        <v>1.122912829299636</v>
       </c>
       <c r="AH88" t="n">
-        <v>0.1858740128425432</v>
+        <v>1.094147232222048</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.2323582769926512</v>
+        <v>1.261217223959586</v>
       </c>
       <c r="AJ88" t="n">
-        <v>4.89892578125</v>
+        <v>9.119140625</v>
       </c>
       <c r="AK88" t="n">
-        <v>4.31884765625</v>
+        <v>8.119140625</v>
       </c>
       <c r="AL88" t="n">
-        <v>5.39892578125</v>
+        <v>9.35888671875</v>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(29.593999999999998), 'mean_duration_us': np.float64(4.932333333333333), 'median_duration_us': np.float64(4.898999999999999), 'std_dev_duration_us': np.float64(0.3499841266241783), 'min_duration_us': np.float64(4.319), 'max_duration_us': np.float64(5.399)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_BBS_BH_Bias_HAS_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(26.597), 'mean_duration_us': np.float64(8.865666666666668), 'median_duration_us': np.float64(9.119), 'std_dev_duration_us': np.float64(0.5369874817493938), 'min_duration_us': np.float64(8.119), 'max_duration_us': np.float64(9.359)}]</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.93)}]</t>
+          <t>[{'name': 'Cijk_Ailk_Bljk_BBS_BH_Bias_HAS_SAV_UserArgs_MT16x16x256_MI16x16x...', 'stream': 0, 'mean_duration_us': np.float64(8.87)}]</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 128, 28, 28), 'shape_in2': (10, 128, 28, 28), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (100352, 784, 28, 1), 'stride_input2': (100352, 784, 28, 1), 'stride_output': None}</t>
+          <t>{'M': 10, 'N': 512, 'K': 1000, 'bias': False, 'stride_A': (1000, 1), 'stride_B': (512, 1), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1, 'transpose': (False, False)}</t>
         </is>
       </c>
       <c r="AP88" t="b">
         <v>1</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.1411187947034128</v>
+        <v>0.1269502185755035</v>
       </c>
       <c r="AR88" t="n">
-        <v>97.55222096259659</v>
+        <v>97.59002474400083</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>aten::mm</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEMM</t>
+          <t>elementwise</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -38632,147 +39642,147 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>((10, 1000), (1000, 512))</t>
+          <t>((10, 256, 14, 14), (10, 256, 14, 14), ())</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>((1000, 1), (512, 1))</t>
+          <t>((50176, 196, 14, 1), (50176, 196, 14, 1), ())</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>('', '')</t>
+          <t>('', '', '1')</t>
         </is>
       </c>
       <c r="J89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>16</v>
+        <v>556</v>
       </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>438.926</v>
+        <v>45.619</v>
       </c>
       <c r="N89" t="n">
-        <v>146.3086666666667</v>
+        <v>7.603166666666667</v>
       </c>
       <c r="O89" t="n">
-        <v>166.7726001186446</v>
+        <v>2.697739825607108</v>
       </c>
       <c r="P89" t="n">
-        <v>0.01024</v>
+        <v>0.00050176</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.005401611328125</v>
+        <v>2.87109375</v>
       </c>
       <c r="R89" t="n">
-        <v>9.713158294126574</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>matrix_bf16</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="T89" t="n">
-        <v>0.1193665053856046</v>
+        <v>0.6952010846285724</v>
       </c>
       <c r="U89" t="n">
-        <v>0.009195732100480506</v>
+        <v>0.01428130609525998</v>
       </c>
       <c r="V89" t="n">
-        <v>1.15942576182709</v>
+        <v>0.1158668474380954</v>
       </c>
       <c r="W89" t="n">
-        <v>0.08931960152234825</v>
+        <v>0.002380217682543333</v>
       </c>
       <c r="X89" t="n">
-        <v>8.86572265625</v>
+        <v>4.33203125</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.6575774436567361</v>
+        <v>0.09015475637167203</v>
       </c>
       <c r="Z89" t="n">
-        <v>26.59716796875</v>
+        <v>25.9921875</v>
       </c>
       <c r="AA89" t="n">
-        <v>58.159</v>
+        <v>6.495</v>
       </c>
       <c r="AB89" t="n">
-        <v>42.109</v>
+        <v>5.29</v>
       </c>
       <c r="AC89" t="n">
-        <v>338.658</v>
+        <v>12.43</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.1156073848789891</v>
+        <v>0.7004151067592712</v>
       </c>
       <c r="AE89" t="n">
-        <v>0.1126458767673606</v>
+        <v>0.6721494472909626</v>
       </c>
       <c r="AF89" t="n">
-        <v>0.1298462545104643</v>
+        <v>0.710243852090773</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.122912829299636</v>
+        <v>0.1167358511265452</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.094147232222048</v>
+        <v>0.1120249078818271</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.261217223959586</v>
+        <v>0.1183739753484622</v>
       </c>
       <c r="AJ89" t="n">
-        <v>9.119140625</v>
+        <v>4.29833984375</v>
       </c>
       <c r="AK89" t="n">
-        <v>8.119140625</v>
+        <v>4.23876953125</v>
       </c>
       <c r="AL89" t="n">
-        <v>9.35888671875</v>
+        <v>4.47900390625</v>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_BBS_BH_Bias_HAS_SAV_UserArgs_MT16x16x256_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMBSK_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD0_NTM0_NEPBS0_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(26.597), 'mean_duration_us': np.float64(8.865666666666668), 'median_duration_us': np.float64(9.119), 'std_dev_duration_us': np.float64(0.5369874817493938), 'min_duration_us': np.float64(8.119), 'max_duration_us': np.float64(9.359)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(25.993), 'mean_duration_us': np.float64(4.332166666666667), 'median_duration_us': np.float64(4.2985), 'std_dev_duration_us': np.float64(0.08222006378548305), 'min_duration_us': np.float64(4.239), 'max_duration_us': np.float64(4.479)}]</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>[{'name': 'Cijk_Ailk_Bljk_BBS_BH_Bias_HAS_SAV_UserArgs_MT16x16x256_MI16x16x...', 'stream': 0, 'mean_duration_us': np.float64(8.87)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.33)}]</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>{'M': 10, 'N': 512, 'K': 1000, 'bias': False, 'stride_A': (1000, 1), 'stride_B': (512, 1), 'dtype_A_B': ('c10::BFloat16', 'c10::BFloat16'), 'B': 1, 'transpose': (False, False)}</t>
+          <t>{'shape_in1': (10, 256, 14, 14), 'shape_in2': (10, 256, 14, 14), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (50176, 196, 14, 1), 'stride_input2': (50176, 196, 14, 1), 'stride_output': None}</t>
         </is>
       </c>
       <c r="AP89" t="b">
         <v>1</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.1268315849042124</v>
+        <v>0.1240626027649795</v>
       </c>
       <c r="AR89" t="n">
-        <v>97.6790525475008</v>
+        <v>97.71408734676581</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::sum</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>elementwise</t>
+          <t>reduce</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -38792,50 +39802,50 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>((10, 256, 14, 14), (10, 256, 14, 14), ())</t>
+          <t>((10, 1000), (), (), ())</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', 'Scalar')</t>
+          <t>('c10::BFloat16', 'ScalarList', 'Scalar', '')</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>((50176, 196, 14, 1), (50176, 196, 14, 1), ())</t>
+          <t>((1000, 1), (), (), ())</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>('', '', '1')</t>
+          <t>('', '[0]', 'True', '')</t>
         </is>
       </c>
       <c r="J90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>556</v>
+        <v>26</v>
       </c>
       <c r="L90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>45.619</v>
+        <v>39.02</v>
       </c>
       <c r="N90" t="n">
-        <v>7.603166666666667</v>
+        <v>13.00666666666667</v>
       </c>
       <c r="O90" t="n">
-        <v>2.697739825607108</v>
+        <v>3.703138308696197</v>
       </c>
       <c r="P90" t="n">
-        <v>0.00050176</v>
+        <v>1e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.87109375</v>
+        <v>0.01907539367675781</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.4999500049995</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -38843,91 +39853,91 @@
         </is>
       </c>
       <c r="T90" t="n">
-        <v>0.6952010846285724</v>
+        <v>0.002508129256082006</v>
       </c>
       <c r="U90" t="n">
-        <v>0.01428130609525998</v>
+        <v>0.0001128074518469964</v>
       </c>
       <c r="V90" t="n">
-        <v>0.1158668474380954</v>
+        <v>0.001253939234117592</v>
       </c>
       <c r="W90" t="n">
-        <v>0.002380217682543333</v>
+        <v>5.639808611488654e-05</v>
       </c>
       <c r="X90" t="n">
-        <v>4.33203125</v>
+        <v>7.985677083333333</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.09015475637167203</v>
+        <v>0.3606049870712312</v>
       </c>
       <c r="Z90" t="n">
-        <v>25.9921875</v>
+        <v>23.95703125</v>
       </c>
       <c r="AA90" t="n">
-        <v>6.495</v>
+        <v>11.16</v>
       </c>
       <c r="AB90" t="n">
-        <v>5.29</v>
+        <v>10.59</v>
       </c>
       <c r="AC90" t="n">
-        <v>12.43</v>
+        <v>17.27</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.7004151067592712</v>
+        <v>0.00251313472392638</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.6721494472909626</v>
+        <v>0.002392902389158245</v>
       </c>
       <c r="AF90" t="n">
-        <v>0.710243852090773</v>
+        <v>0.002618350655161394</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.1167358511265452</v>
+        <v>0.001256441717791411</v>
       </c>
       <c r="AH90" t="n">
-        <v>0.1120249078818271</v>
+        <v>0.001196331561422981</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.1183739753484622</v>
+        <v>0.001309044423138383</v>
       </c>
       <c r="AJ90" t="n">
-        <v>4.29833984375</v>
+        <v>7.958984375</v>
       </c>
       <c r="AK90" t="n">
-        <v>4.23876953125</v>
+        <v>7.63916015625</v>
       </c>
       <c r="AL90" t="n">
-        <v>4.47900390625</v>
+        <v>8.35888671875</v>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 6, 'total_duration_us': np.float64(25.993), 'mean_duration_us': np.float64(4.332166666666667), 'median_duration_us': np.float64(4.2985), 'std_dev_duration_us': np.float64(0.08222006378548305), 'min_duration_us': np.float64(4.239), 'max_duration_us': np.float64(4.479)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(23.956999999999997), 'mean_duration_us': np.float64(7.985666666666666), 'median_duration_us': np.float64(7.959), 'std_dev_duration_us': np.float64(0.2945429604583269), 'min_duration_us': np.float64(7.639), 'max_duration_us': np.float64(8.359)}]</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.33)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.99)}]</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 256, 14, 14), 'shape_in2': (10, 256, 14, 14), 'dtype_in1_in2_out': ('c10::BFloat16', 'c10::BFloat16', None), 'stride_input1': (50176, 196, 14, 1), 'stride_input2': (50176, 196, 14, 1), 'stride_output': None}</t>
+          <t>{'num_input_elems': 10000, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'sum'}</t>
         </is>
       </c>
       <c r="AP90" t="b">
         <v>1</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.1239466675409123</v>
+        <v>0.1143486538559693</v>
       </c>
       <c r="AR90" t="n">
-        <v>97.80299921504171</v>
+        <v>97.82843600062178</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>aten::sum</t>
+          <t>aten::mean</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -38947,12 +39957,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>thread 639 (pt_autograd_0)</t>
+          <t>thread 542 (python3)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>((10, 1000), (), (), ())</t>
+          <t>((10, 512, 7, 7), (), (), ())</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -38962,103 +39972,137 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>((1000, 1), (), (), ())</t>
+          <t>((25088, 49, 7, 1), (), (), ())</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>('', '[0]', 'True', '')</t>
+          <t>('', '[-1, -2]', 'True', '')</t>
         </is>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>26</v>
+        <v>6390</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>39.02</v>
+        <v>37.98</v>
       </c>
       <c r="N91" t="n">
-        <v>13.00666666666667</v>
+        <v>12.66</v>
       </c>
       <c r="O91" t="n">
-        <v>3.703138308696197</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
+        <v>1.301499135612468</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.00025088</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.4785175323486328</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.49999800702325</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>0.06830178233786818</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0.003438278962410554</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0.0341507550450699</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0.001719132628795248</v>
+      </c>
       <c r="X91" t="n">
-        <v>7.985677083333333</v>
+        <v>7.359049479166667</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.3606049870712312</v>
+        <v>0.3813852705988001</v>
       </c>
       <c r="Z91" t="n">
-        <v>23.95703125</v>
+        <v>22.0771484375</v>
       </c>
       <c r="AA91" t="n">
-        <v>11.16</v>
+        <v>12.51</v>
       </c>
       <c r="AB91" t="n">
-        <v>10.59</v>
+        <v>11.44</v>
       </c>
       <c r="AC91" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="AD91" t="inlineStr"/>
-      <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
-      <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
+        <v>14.03</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0.07008652134770155</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0.06433812772351616</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>0.07048069794238684</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>0.03504312099304324</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0.03216893563736539</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>0.0352402085048011</v>
+      </c>
       <c r="AJ91" t="n">
-        <v>7.958984375</v>
+        <v>7.1591796875</v>
       </c>
       <c r="AK91" t="n">
-        <v>7.63916015625</v>
+        <v>7.119140625</v>
       </c>
       <c r="AL91" t="n">
-        <v>8.35888671875</v>
+        <v>7.798828125</v>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::func_wrapper_t&lt;c10::BFloat16, at::native::sum_functor&lt;c10::BFloat16, float, c10::BFloat16&gt;::operator()(at::TensorIterator&amp;)::{lambda(float, float)#1}&gt;, unsigned int, c10::BFloat16, 4, 8&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(23.956999999999997), 'mean_duration_us': np.float64(7.985666666666666), 'median_duration_us': np.float64(7.959), 'std_dev_duration_us': np.float64(0.2945429604583269), 'min_duration_us': np.float64(7.639), 'max_duration_us': np.float64(8.359)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(22.076999999999998), 'mean_duration_us': np.float64(7.358999999999999), 'median_duration_us': np.float64(7.159), 'std_dev_duration_us': np.float64(0.31155523854794487), 'min_duration_us': np.float64(7.119), 'max_duration_us': np.float64(7.799)}]</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.99)}]</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr"/>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.36)}]</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 250880, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'mean'}</t>
+        </is>
+      </c>
       <c r="AP91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.1142417962170747</v>
+        <v>0.1053758363656407</v>
       </c>
       <c r="AR91" t="n">
-        <v>97.91724101125878</v>
+        <v>97.93381183698742</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>aten::mean</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>reduce</t>
+          <t>elementwise</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -39073,107 +40117,141 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>thread 542 (python3)</t>
+          <t>thread 639 (pt_autograd_0)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>((10, 512, 7, 7), (), (), ())</t>
+          <t>((256, 256, 3, 3), (), (256, 256, 3, 3))</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'ScalarList', 'Scalar', '')</t>
+          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>((25088, 49, 7, 1), (), (), ())</t>
+          <t>((2304, 9, 3, 1), (), (2304, 9, 3, 1))</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>('', '[-1, -2]', 'True', '')</t>
+          <t>('', '', '')</t>
         </is>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>6390</v>
+        <v>675</v>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M92" t="n">
-        <v>37.98</v>
+        <v>47.26</v>
       </c>
       <c r="N92" t="n">
-        <v>12.66</v>
+        <v>5.251111111111111</v>
       </c>
       <c r="O92" t="n">
-        <v>1.301499135612468</v>
-      </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+        <v>1.266821262495665</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.000589824</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>2.250007629394531</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.249999152292371</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
+        <v>1.080930706018675</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0.3345349679931722</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0.2702317601914628</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0.0836334584104485</v>
+      </c>
       <c r="X92" t="n">
-        <v>7.359049479166667</v>
+        <v>2.443413628472222</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.3813852705988001</v>
+        <v>0.9494697472681765</v>
       </c>
       <c r="Z92" t="n">
-        <v>22.0771484375</v>
+        <v>21.99072265625</v>
       </c>
       <c r="AA92" t="n">
-        <v>12.51</v>
+        <v>4.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>11.44</v>
+        <v>4.13</v>
       </c>
       <c r="AC92" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
-      <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
+        <v>8.17</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>1.283020337758896</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>0.6145833874332232</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>1.372296106787845</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>0.3207539968135953</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>0.1536453258712796</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>0.3430728633910821</v>
+      </c>
       <c r="AJ92" t="n">
-        <v>7.1591796875</v>
+        <v>1.8388671875</v>
       </c>
       <c r="AK92" t="n">
-        <v>7.119140625</v>
+        <v>1.71923828125</v>
       </c>
       <c r="AL92" t="n">
-        <v>7.798828125</v>
+        <v>3.8388671875</v>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(22.076999999999998), 'mean_duration_us': np.float64(7.358999999999999), 'median_duration_us': np.float64(7.159), 'std_dev_duration_us': np.float64(0.31155523854794487), 'min_duration_us': np.float64(7.119), 'max_duration_us': np.float64(7.799)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(21.991), 'mean_duration_us': np.float64(2.4434444444444443), 'median_duration_us': np.float64(1.839), 'std_dev_duration_us': np.float64(0.895111552465962), 'min_duration_us': np.float64(1.719), 'max_duration_us': np.float64(3.839)}]</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(7.36)}]</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr"/>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.44)}]</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>{'shape_in1': (256, 256, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (2304, 9, 3, 1), 'stride_input2': (), 'stride_output': (2304, 9, 3, 1)}</t>
+        </is>
+      </c>
       <c r="AP92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.1052773637322439</v>
+        <v>0.1049633198212801</v>
       </c>
       <c r="AR92" t="n">
-        <v>98.02251837499102</v>
+        <v>98.0387751568087</v>
       </c>
     </row>
     <row r="93">
@@ -39204,7 +40282,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>((256, 256, 3, 3), (), (256, 256, 3, 3))</t>
+          <t>((128, 128, 3, 3), (), (128, 128, 3, 3))</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -39214,7 +40292,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>((2304, 9, 3, 1), (), (2304, 9, 3, 1))</t>
+          <t>((1152, 9, 3, 1), (), (1152, 9, 3, 1))</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -39226,28 +40304,28 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>675</v>
+        <v>1075</v>
       </c>
       <c r="L93" t="n">
         <v>9</v>
       </c>
       <c r="M93" t="n">
-        <v>47.26</v>
+        <v>45</v>
       </c>
       <c r="N93" t="n">
-        <v>5.251111111111111</v>
+        <v>5</v>
       </c>
       <c r="O93" t="n">
-        <v>1.266821262495665</v>
+        <v>0.5905929224093363</v>
       </c>
       <c r="P93" t="n">
-        <v>0.000589824</v>
+        <v>0.000147456</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.250007629394531</v>
+        <v>0.5625076293945312</v>
       </c>
       <c r="R93" t="n">
-        <v>0.249999152292371</v>
+        <v>0.2499966092039767</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -39255,91 +40333,91 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>1.080930706018675</v>
+        <v>0.2733472121251077</v>
       </c>
       <c r="U93" t="n">
-        <v>0.3345349679931722</v>
+        <v>0.0840759242798106</v>
       </c>
       <c r="V93" t="n">
-        <v>0.2702317601914628</v>
+        <v>0.06833587616663707</v>
       </c>
       <c r="W93" t="n">
-        <v>0.0836334584104485</v>
+        <v>0.02101869598564295</v>
       </c>
       <c r="X93" t="n">
-        <v>2.443413628472222</v>
+        <v>2.407877604166667</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.9494697472681765</v>
+        <v>0.9181949417968699</v>
       </c>
       <c r="Z93" t="n">
-        <v>21.99072265625</v>
+        <v>21.6708984375</v>
       </c>
       <c r="AA93" t="n">
-        <v>4.8</v>
+        <v>4.63</v>
       </c>
       <c r="AB93" t="n">
-        <v>4.13</v>
+        <v>4.39</v>
       </c>
       <c r="AC93" t="n">
-        <v>8.17</v>
+        <v>5.86</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.283020337758896</v>
+        <v>0.3139230602910603</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.6145833874332232</v>
+        <v>0.1569207503247597</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.372296106787845</v>
+        <v>0.3512579052050014</v>
       </c>
       <c r="AG93" t="n">
-        <v>0.3207539968135953</v>
+        <v>0.07847970062370062</v>
       </c>
       <c r="AH93" t="n">
-        <v>0.1536453258712796</v>
+        <v>0.03922965549493375</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.3430728633910821</v>
+        <v>0.08781328525734224</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1.8388671875</v>
+        <v>1.87890625</v>
       </c>
       <c r="AK93" t="n">
-        <v>1.71923828125</v>
+        <v>1.67919921875</v>
       </c>
       <c r="AL93" t="n">
-        <v>3.8388671875</v>
+        <v>3.7587890625</v>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(21.991), 'mean_duration_us': np.float64(2.4434444444444443), 'median_duration_us': np.float64(1.839), 'std_dev_duration_us': np.float64(0.895111552465962), 'min_duration_us': np.float64(1.719), 'max_duration_us': np.float64(3.839)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(21.670999999999996), 'mean_duration_us': np.float64(2.4078888888888885), 'median_duration_us': np.float64(1.879), 'std_dev_duration_us': np.float64(0.8656974637628507), 'min_duration_us': np.float64(1.679), 'max_duration_us': np.float64(3.759)}]</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.44)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.41)}]</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>{'shape_in1': (256, 256, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (2304, 9, 3, 1), 'stride_input2': (), 'stride_output': (2304, 9, 3, 1)}</t>
+          <t>{'shape_in1': (128, 128, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (1152, 9, 3, 1), 'stride_input2': (), 'stride_output': (1152, 9, 3, 1)}</t>
         </is>
       </c>
       <c r="AP93" t="b">
         <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.1048652326803439</v>
+        <v>0.1034367755469515</v>
       </c>
       <c r="AR93" t="n">
-        <v>98.12738360767136</v>
+        <v>98.14221193235565</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::mse_loss_backward</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -39364,147 +40442,113 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>((128, 128, 3, 3), (), (128, 128, 3, 3))</t>
+          <t>((), (10, 1000), (10, 1000), (), (10, 1000))</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', 'c10::BFloat16')</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>((1152, 9, 3, 1), (), (1152, 9, 3, 1))</t>
+          <t>((), (1000, 1), (1000, 1), (), (1000, 1))</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>('', '', '')</t>
+          <t>('', '', '', '1', '')</t>
         </is>
       </c>
       <c r="J94" t="b">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1075</v>
+        <v>9</v>
       </c>
       <c r="L94" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>45</v>
+        <v>26.05</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>8.683333333333334</v>
       </c>
       <c r="O94" t="n">
-        <v>0.5905929224093363</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0.000147456</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0.5625076293945312</v>
-      </c>
-      <c r="R94" t="n">
-        <v>0.2499966092039767</v>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="T94" t="n">
-        <v>0.2733472121251077</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0.0840759242798106</v>
-      </c>
-      <c r="V94" t="n">
-        <v>0.06833587616663707</v>
-      </c>
-      <c r="W94" t="n">
-        <v>0.02101869598564295</v>
-      </c>
+        <v>2.602428353160435</v>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
       <c r="X94" t="n">
-        <v>2.407877604166667</v>
+        <v>7.118977864583333</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.9181949417968699</v>
+        <v>0.7664773569099081</v>
       </c>
       <c r="Z94" t="n">
-        <v>21.6708984375</v>
+        <v>21.35693359375</v>
       </c>
       <c r="AA94" t="n">
-        <v>4.63</v>
+        <v>7.67</v>
       </c>
       <c r="AB94" t="n">
-        <v>4.39</v>
+        <v>6.74</v>
       </c>
       <c r="AC94" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AD94" t="n">
-        <v>0.3139230602910603</v>
-      </c>
-      <c r="AE94" t="n">
-        <v>0.1569207503247597</v>
-      </c>
-      <c r="AF94" t="n">
-        <v>0.3512579052050014</v>
-      </c>
-      <c r="AG94" t="n">
-        <v>0.07847970062370062</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>0.03922965549493375</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>0.08781328525734224</v>
-      </c>
+        <v>11.64</v>
+      </c>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
       <c r="AJ94" t="n">
-        <v>1.87890625</v>
+        <v>7.47900390625</v>
       </c>
       <c r="AK94" t="n">
-        <v>1.67919921875</v>
+        <v>6.23876953125</v>
       </c>
       <c r="AL94" t="n">
-        <v>3.7587890625</v>
+        <v>7.63916015625</v>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 9, 'total_duration_us': np.float64(21.670999999999996), 'mean_duration_us': np.float64(2.4078888888888885), 'median_duration_us': np.float64(1.879), 'std_dev_duration_us': np.float64(0.8656974637628507), 'min_duration_us': np.float64(1.679), 'max_duration_us': np.float64(3.759)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.357), 'mean_duration_us': np.float64(7.119), 'median_duration_us': np.float64(7.479), 'std_dev_duration_us': np.float64(0.625672971021337), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(7.639)}]</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(2.41)}]</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>{'shape_in1': (128, 128, 3, 3), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'double', 'c10::BFloat16'), 'stride_input1': (1152, 9, 3, 1), 'stride_input2': (), 'stride_output': (1152, 9, 3, 1)}</t>
-        </is>
-      </c>
+          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(7.12)}]</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr"/>
       <c r="AP94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.1033401149459117</v>
+        <v>0.1019381984959693</v>
       </c>
       <c r="AR94" t="n">
-        <v>98.23072372261727</v>
+        <v>98.24415013085162</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>aten::mse_loss_backward</t>
+          <t>aten::mean</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>elementwise</t>
+          <t>reduce</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -39519,107 +40563,141 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>thread 639 (pt_autograd_0)</t>
+          <t>thread 542 (python3)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>((), (10, 1000), (10, 1000), (), (10, 1000))</t>
+          <t>((10, 1000), (), (), (), ())</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', 'c10::BFloat16', 'Scalar', 'c10::BFloat16')</t>
+          <t>('c10::BFloat16', 'ScalarList', 'Scalar', '', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>((), (1000, 1), (1000, 1), (), (1000, 1))</t>
+          <t>((1000, 1), (), (), (), ())</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>('', '', '', '1', '')</t>
+          <t>('', '[]', 'False', '', '')</t>
         </is>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>9</v>
+        <v>6408</v>
       </c>
       <c r="L95" t="n">
         <v>3</v>
       </c>
       <c r="M95" t="n">
-        <v>26.05</v>
+        <v>25.23</v>
       </c>
       <c r="N95" t="n">
-        <v>8.683333333333334</v>
+        <v>8.41</v>
       </c>
       <c r="O95" t="n">
-        <v>2.602428353160435</v>
-      </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+        <v>0.9355212450821205</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.01907539367675781</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.4999500049995</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>0.003323919239960658</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0.000369630530044365</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0.001661793440636265</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0.0001847967853436482</v>
+      </c>
       <c r="X95" t="n">
-        <v>7.118977864583333</v>
+        <v>6.065755208333333</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.7664773569099081</v>
+        <v>0.6504878218749942</v>
       </c>
       <c r="Z95" t="n">
-        <v>21.35693359375</v>
+        <v>18.197265625</v>
       </c>
       <c r="AA95" t="n">
-        <v>7.67</v>
+        <v>7.89</v>
       </c>
       <c r="AB95" t="n">
-        <v>6.74</v>
+        <v>7.85</v>
       </c>
       <c r="AC95" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
+        <v>9.49</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>0.003226535601764335</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>0.003012730455247481</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>0.003732491662870159</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>0.001613106490233144</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>0.001506214606163124</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>0.001866059225512528</v>
+      </c>
       <c r="AJ95" t="n">
-        <v>7.47900390625</v>
+        <v>6.19921875</v>
       </c>
       <c r="AK95" t="n">
-        <v>6.23876953125</v>
+        <v>5.35888671875</v>
       </c>
       <c r="AL95" t="n">
-        <v>7.63916015625</v>
+        <v>6.63916015625</v>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::mse_backward_cuda_kernel(at::TensorIterator&amp;, c10::Scalar const&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16, c10::BFloat16, c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(21.357), 'mean_duration_us': np.float64(7.119), 'median_duration_us': np.float64(7.479), 'std_dev_duration_us': np.float64(0.625672971021337), 'min_duration_us': np.float64(6.239), 'max_duration_us': np.float64(7.639)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4, 4&gt;)', 'stream': 0, 'count': 3, 'total_duration_us': np.float64(18.197000000000003), 'mean_duration_us': np.float64(6.065666666666668), 'median_duration_us': np.float64(6.199), 'std_dev_duration_us': np.float64(0.5309948733797302), 'min_duration_us': np.float64(5.359), 'max_duration_us': np.float64(6.639)}]</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(7.12)}]</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr"/>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;c10:...', 'stream': 0, 'mean_duration_us': np.float64(6.07)}]</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 10000, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'mean'}</t>
+        </is>
+      </c>
       <c r="AP95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.1018429382997438</v>
+        <v>0.0868568733063807</v>
       </c>
       <c r="AR95" t="n">
-        <v>98.33256666091701</v>
+        <v>98.331007004158</v>
       </c>
     </row>
     <row r="96">
@@ -39776,21 +40854,21 @@
         <v>1</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.08525058871872973</v>
+        <v>0.08533032903205207</v>
       </c>
       <c r="AR96" t="n">
-        <v>98.41781724963575</v>
+        <v>98.41633733319004</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>aten::div</t>
+          <t>MeanBackward1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>elementwise</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -39810,50 +40888,50 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>((10, 512, 7, 7), ())</t>
+          <t>((10, 512, 1, 1),)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'Scalar')</t>
+          <t>('c10::BFloat16',)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>((512, 1, 0, 0), ())</t>
+          <t>((512, 1, 1, 1),)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>('', '49')</t>
+          <t>('',)</t>
         </is>
       </c>
       <c r="J97" t="b">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
       </c>
       <c r="M97" t="n">
-        <v>38.229</v>
+        <v>57.239</v>
       </c>
       <c r="N97" t="n">
-        <v>12.743</v>
+        <v>19.07966666666667</v>
       </c>
       <c r="O97" t="n">
-        <v>3.840914864976832</v>
+        <v>6.045837438546735</v>
       </c>
       <c r="P97" t="n">
         <v>0.00025088</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.9570350646972656</v>
+        <v>0.4785175323486328</v>
       </c>
       <c r="R97" t="n">
-        <v>0.249999003511625</v>
+        <v>0.49999800702325</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -39861,10 +40939,10 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>0.1702785883097112</v>
+        <v>0.08513929415485562</v>
       </c>
       <c r="U97" t="n">
-        <v>0.009476088609910798</v>
+        <v>0.004738044304955399</v>
       </c>
       <c r="V97" t="n">
         <v>0.04256947739679404</v>
@@ -39882,22 +40960,22 @@
         <v>17.71630859375</v>
       </c>
       <c r="AA97" t="n">
-        <v>11.51</v>
+        <v>17.25</v>
       </c>
       <c r="AB97" t="n">
-        <v>9.67</v>
+        <v>14.16</v>
       </c>
       <c r="AC97" t="n">
-        <v>17.049</v>
+        <v>25.829</v>
       </c>
       <c r="AD97" t="n">
-        <v>0.1684052074729597</v>
+        <v>0.08420260373647985</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.1618791077504726</v>
+        <v>0.0809395538752363</v>
       </c>
       <c r="AF97" t="n">
-        <v>0.1805514497057015</v>
+        <v>0.09027572485285074</v>
       </c>
       <c r="AG97" t="n">
         <v>0.04210113405440839</v>
@@ -39929,17 +41007,17 @@
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>{'shape_in1': (10, 512, 7, 7), 'shape_in2': (), 'dtype_in1_in2_out': ('c10::BFloat16', 'Scalar', None), 'stride_input1': (512, 1, 0, 0), 'stride_input2': (), 'stride_output': None}</t>
+          <t>{'num_input_elems': 250880, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'mean'}</t>
         </is>
       </c>
       <c r="AP97" t="b">
         <v>1</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.08448220879145851</v>
+        <v>0.08456123039002392</v>
       </c>
       <c r="AR97" t="n">
-        <v>98.5022994584272</v>
+        <v>98.50089856358007</v>
       </c>
     </row>
     <row r="98">
@@ -40096,10 +41174,10 @@
         <v>1</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.0842819643255636</v>
+        <v>0.08436079862270747</v>
       </c>
       <c r="AR98" t="n">
-        <v>98.58658142275277</v>
+        <v>98.58525936220278</v>
       </c>
     </row>
     <row r="99">
@@ -40256,10 +41334,10 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.08427963590154157</v>
+        <v>0.08435846802076194</v>
       </c>
       <c r="AR99" t="n">
-        <v>98.67086105865431</v>
+        <v>98.66961783022354</v>
       </c>
     </row>
     <row r="100">
@@ -40416,10 +41494,10 @@
         <v>1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.07914313250893462</v>
+        <v>0.07921716012890093</v>
       </c>
       <c r="AR100" t="n">
-        <v>98.75000419116324</v>
+        <v>98.74883499035245</v>
       </c>
     </row>
     <row r="101">
@@ -40576,10 +41654,10 @@
         <v>1</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.07132428464294456</v>
+        <v>0.07139099879577797</v>
       </c>
       <c r="AR101" t="n">
-        <v>98.82132847580618</v>
+        <v>98.82022598914823</v>
       </c>
     </row>
     <row r="102">
@@ -40736,10 +41814,10 @@
         <v>1</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.07075149233352421</v>
+        <v>0.07081767071717517</v>
       </c>
       <c r="AR102" t="n">
-        <v>98.89207996813971</v>
+        <v>98.8910436598654</v>
       </c>
     </row>
     <row r="103">
@@ -40896,10 +41974,10 @@
         <v>1</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.06960823613870552</v>
+        <v>0.06967334516191508</v>
       </c>
       <c r="AR103" t="n">
-        <v>98.96168820427842</v>
+        <v>98.96071700502732</v>
       </c>
     </row>
     <row r="104">
@@ -41022,10 +42100,10 @@
         <v>0</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.06864892544162753</v>
+        <v>0.06871313716035264</v>
       </c>
       <c r="AR104" t="n">
-        <v>99.03033712972004</v>
+        <v>99.02943014218768</v>
       </c>
     </row>
     <row r="105">
@@ -41182,10 +42260,10 @@
         <v>1</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.06827172075005802</v>
+        <v>0.06833557964517517</v>
       </c>
       <c r="AR105" t="n">
-        <v>99.0986088504701</v>
+        <v>99.09776572183286</v>
       </c>
     </row>
     <row r="106">
@@ -41342,10 +42420,10 @@
         <v>1</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.06808078998025124</v>
+        <v>0.0681444702856409</v>
       </c>
       <c r="AR106" t="n">
-        <v>99.16668964045036</v>
+        <v>99.1659101921185</v>
       </c>
     </row>
     <row r="107">
@@ -41502,10 +42580,10 @@
         <v>1</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.06617381070620541</v>
+        <v>0.06623570729224373</v>
       </c>
       <c r="AR107" t="n">
-        <v>99.23286345115656</v>
+        <v>99.23214589941075</v>
       </c>
     </row>
     <row r="108">
@@ -41628,10 +42706,10 @@
         <v>0</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.06579194916659184</v>
+        <v>0.06585348857317519</v>
       </c>
       <c r="AR108" t="n">
-        <v>99.29865540032316</v>
+        <v>99.29799938798392</v>
       </c>
     </row>
     <row r="109">
@@ -41788,10 +42866,10 @@
         <v>1</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.06464636454775113</v>
+        <v>0.06470683241596956</v>
       </c>
       <c r="AR109" t="n">
-        <v>99.36330176487091</v>
+        <v>99.36270622039989</v>
       </c>
     </row>
     <row r="110">
@@ -41948,10 +43026,10 @@
         <v>1</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.06312124681331888</v>
+        <v>0.06318028814164094</v>
       </c>
       <c r="AR110" t="n">
-        <v>99.42642301168424</v>
+        <v>99.42588650854152</v>
       </c>
     </row>
     <row r="111">
@@ -42108,10 +43186,10 @@
         <v>1</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.06255078292792056</v>
+        <v>0.06260929066498366</v>
       </c>
       <c r="AR111" t="n">
-        <v>99.48897379461215</v>
+        <v>99.4884957992065</v>
       </c>
     </row>
     <row r="112">
@@ -42268,10 +43346,10 @@
         <v>1</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.06254845450389852</v>
+        <v>0.06260696006303812</v>
       </c>
       <c r="AR112" t="n">
-        <v>99.55152224911605</v>
+        <v>99.55110275926954</v>
       </c>
     </row>
     <row r="113">
@@ -42394,10 +43472,10 @@
         <v>0</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.05816170364638654</v>
+        <v>0.05821610599764097</v>
       </c>
       <c r="AR113" t="n">
-        <v>99.60968395276244</v>
+        <v>99.60931886526718</v>
       </c>
     </row>
     <row r="114">
@@ -42554,10 +43632,10 @@
         <v>1</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.05530239894732882</v>
+        <v>0.05535412680851798</v>
       </c>
       <c r="AR114" t="n">
-        <v>99.66498635170977</v>
+        <v>99.66467299207571</v>
       </c>
     </row>
     <row r="115">
@@ -42714,10 +43792,10 @@
         <v>1</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.05301355813366943</v>
+        <v>0.05306314509605227</v>
       </c>
       <c r="AR115" t="n">
-        <v>99.71799990984344</v>
+        <v>99.71773613717176</v>
       </c>
     </row>
     <row r="116">
@@ -42874,10 +43952,10 @@
         <v>1</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.05148844039923717</v>
+        <v>0.05153660082172363</v>
       </c>
       <c r="AR116" t="n">
-        <v>99.76948835024268</v>
+        <v>99.76927273799348</v>
       </c>
     </row>
     <row r="117">
@@ -43034,10 +44112,10 @@
         <v>1</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.05109959358755749</v>
+        <v>0.05114739029681847</v>
       </c>
       <c r="AR117" t="n">
-        <v>99.82058794383023</v>
+        <v>99.82042012829029</v>
       </c>
     </row>
     <row r="118">
@@ -43194,10 +44272,10 @@
         <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.04614703569269125</v>
+        <v>0.04619019995865512</v>
       </c>
       <c r="AR118" t="n">
-        <v>99.86673497952293</v>
+        <v>99.86661032824895</v>
       </c>
     </row>
     <row r="119">
@@ -43354,10 +44432,10 @@
         <v>1</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.04061470021633853</v>
+        <v>0.04065268973605234</v>
       </c>
       <c r="AR119" t="n">
-        <v>99.90734967973927</v>
+        <v>99.907263017985</v>
       </c>
     </row>
     <row r="120">
@@ -43514,10 +44592,10 @@
         <v>1</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.02402235063532446</v>
+        <v>0.02404482027213507</v>
       </c>
       <c r="AR120" t="n">
-        <v>99.93137203037459</v>
+        <v>99.93130783825714</v>
       </c>
     </row>
     <row r="121">
@@ -43640,10 +44718,10 @@
         <v>0</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.02383141986551768</v>
+        <v>0.0238537109126008</v>
       </c>
       <c r="AR121" t="n">
-        <v>99.95520345024011</v>
+        <v>99.95516154916974</v>
       </c>
     </row>
     <row r="122">
@@ -43800,10 +44878,10 @@
         <v>1</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.02325629913207529</v>
+        <v>0.02327805223205244</v>
       </c>
       <c r="AR122" t="n">
-        <v>99.97845974937218</v>
+        <v>99.9784396014018</v>
       </c>
     </row>
     <row r="123">
@@ -43960,10 +45038,10 @@
         <v>1</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.02154025062783625</v>
+        <v>0.02156039859818954</v>
       </c>
       <c r="AR123" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
     </row>
   </sheetData>
